--- a/research/traditional_assets/database/data/egypt/egypt_furn_home_furnishings.xlsx
+++ b/research/traditional_assets/database/data/egypt/egypt_furn_home_furnishings.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1798232631958509</v>
+        <v>0.1794535358536603</v>
       </c>
       <c r="C2">
-        <v>530.4111201651059</v>
+        <v>526.6668450619584</v>
       </c>
       <c r="D2">
-        <v>457.9111201651059</v>
+        <v>459.1778450619583</v>
       </c>
       <c r="E2">
-        <v>-174</v>
+        <v>-168.989</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.011</v>
       </c>
       <c r="G2">
         <v>72.5</v>
@@ -1451,28 +1451,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2520533</v>
       </c>
       <c r="N2">
-        <v>56.7111111111111</v>
+        <v>56.4590578111111</v>
       </c>
       <c r="O2">
-        <v>12.76</v>
+        <v>12.7032880075</v>
       </c>
       <c r="P2">
-        <v>43.9511111111111</v>
+        <v>43.7557698036111</v>
       </c>
       <c r="Q2">
-        <v>65.35111111111109</v>
+        <v>65.15576980361109</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1798232631958509</v>
+        <v>0.1808724352057174</v>
       </c>
       <c r="T2">
-        <v>0.9344695036460947</v>
+        <v>0.9417847952150413</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>224.9965031646525</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1794535358536603</v>
+        <v>0.1790838085114695</v>
       </c>
       <c r="C3">
-        <v>526.6668450619584</v>
+        <v>522.9295977116134</v>
       </c>
       <c r="D3">
-        <v>459.1778450619583</v>
+        <v>460.4515977116135</v>
       </c>
       <c r="E3">
-        <v>-168.989</v>
+        <v>-163.978</v>
       </c>
       <c r="F3">
-        <v>5.011</v>
+        <v>10.022</v>
       </c>
       <c r="G3">
         <v>72.5</v>
@@ -1533,28 +1533,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M3">
-        <v>0.2520533</v>
+        <v>0.5041066</v>
       </c>
       <c r="N3">
-        <v>56.4590578111111</v>
+        <v>56.2070045111111</v>
       </c>
       <c r="O3">
-        <v>12.7032880075</v>
+        <v>12.646576015</v>
       </c>
       <c r="P3">
-        <v>43.7557698036111</v>
+        <v>43.5604284961111</v>
       </c>
       <c r="Q3">
-        <v>65.15576980361109</v>
+        <v>64.96042849611109</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1808724352057174</v>
+        <v>0.1819430188892547</v>
       </c>
       <c r="T3">
-        <v>0.9417847952150413</v>
+        <v>0.9492493784486604</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>224.9965031646525</v>
+        <v>112.4982515823262</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1790838085114695</v>
+        <v>0.1787140811692789</v>
       </c>
       <c r="C4">
-        <v>522.9295977116134</v>
+        <v>519.1994367614093</v>
       </c>
       <c r="D4">
-        <v>460.4515977116135</v>
+        <v>461.7324367614093</v>
       </c>
       <c r="E4">
-        <v>-163.978</v>
+        <v>-158.967</v>
       </c>
       <c r="F4">
-        <v>10.022</v>
+        <v>15.033</v>
       </c>
       <c r="G4">
         <v>72.5</v>
@@ -1615,28 +1615,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M4">
-        <v>0.5041066</v>
+        <v>0.7561598999999999</v>
       </c>
       <c r="N4">
-        <v>56.2070045111111</v>
+        <v>55.9549512111111</v>
       </c>
       <c r="O4">
-        <v>12.646576015</v>
+        <v>12.5898640225</v>
       </c>
       <c r="P4">
-        <v>43.5604284961111</v>
+        <v>43.3650871886111</v>
       </c>
       <c r="Q4">
-        <v>64.96042849611109</v>
+        <v>64.76508718861109</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1819430188892547</v>
+        <v>0.1830356764631741</v>
       </c>
       <c r="T4">
-        <v>0.9492493784486604</v>
+        <v>0.9568678706149314</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>112.4982515823262</v>
+        <v>74.9988343882175</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1787140811692789</v>
+        <v>0.1783443538270882</v>
       </c>
       <c r="C5">
-        <v>519.1994367614093</v>
+        <v>515.4764215130625</v>
       </c>
       <c r="D5">
-        <v>461.7324367614093</v>
+        <v>463.0204215130625</v>
       </c>
       <c r="E5">
-        <v>-158.967</v>
+        <v>-153.956</v>
       </c>
       <c r="F5">
-        <v>15.033</v>
+        <v>20.044</v>
       </c>
       <c r="G5">
         <v>72.5</v>
@@ -1697,28 +1697,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M5">
-        <v>0.7561598999999999</v>
+        <v>1.0082132</v>
       </c>
       <c r="N5">
-        <v>55.9549512111111</v>
+        <v>55.7028979111111</v>
       </c>
       <c r="O5">
-        <v>12.5898640225</v>
+        <v>12.53315203</v>
       </c>
       <c r="P5">
-        <v>43.3650871886111</v>
+        <v>43.1697458811111</v>
       </c>
       <c r="Q5">
-        <v>64.76508718861109</v>
+        <v>64.5697458811111</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1830356764631741</v>
+        <v>0.1841510977365503</v>
       </c>
       <c r="T5">
-        <v>0.9568678706149314</v>
+        <v>0.9646450813679998</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>74.9988343882175</v>
+        <v>56.24912579116312</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1783443538270882</v>
+        <v>0.1779746264848976</v>
       </c>
       <c r="C6">
-        <v>515.4764215130625</v>
+        <v>511.7606119318195</v>
       </c>
       <c r="D6">
-        <v>463.0204215130625</v>
+        <v>464.3156119318195</v>
       </c>
       <c r="E6">
-        <v>-153.956</v>
+        <v>-148.945</v>
       </c>
       <c r="F6">
-        <v>20.044</v>
+        <v>25.055</v>
       </c>
       <c r="G6">
         <v>72.5</v>
@@ -1779,28 +1779,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M6">
-        <v>1.0082132</v>
+        <v>1.2602665</v>
       </c>
       <c r="N6">
-        <v>55.7028979111111</v>
+        <v>55.4508446111111</v>
       </c>
       <c r="O6">
-        <v>12.53315203</v>
+        <v>12.4764400375</v>
       </c>
       <c r="P6">
-        <v>43.1697458811111</v>
+        <v>42.9744045736111</v>
       </c>
       <c r="Q6">
-        <v>64.5697458811111</v>
+        <v>64.3744045736111</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1841510977365503</v>
+        <v>0.1852900015630501</v>
       </c>
       <c r="T6">
-        <v>0.9646450813679998</v>
+        <v>0.9725860228737643</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>56.24912579116312</v>
+        <v>44.99930063293049</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1779746264848976</v>
+        <v>0.1776048991427069</v>
       </c>
       <c r="C7">
-        <v>511.7606119318195</v>
+        <v>508.0520686557636</v>
       </c>
       <c r="D7">
-        <v>464.3156119318195</v>
+        <v>465.6180686557636</v>
       </c>
       <c r="E7">
-        <v>-148.945</v>
+        <v>-143.934</v>
       </c>
       <c r="F7">
-        <v>25.055</v>
+        <v>30.066</v>
       </c>
       <c r="G7">
         <v>72.5</v>
@@ -1861,28 +1861,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M7">
-        <v>1.2602665</v>
+        <v>1.5123198</v>
       </c>
       <c r="N7">
-        <v>55.4508446111111</v>
+        <v>55.1987913111111</v>
       </c>
       <c r="O7">
-        <v>12.4764400375</v>
+        <v>12.419728045</v>
       </c>
       <c r="P7">
-        <v>42.9744045736111</v>
+        <v>42.7790632661111</v>
       </c>
       <c r="Q7">
-        <v>64.3744045736111</v>
+        <v>64.1790632661111</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1852900015630501</v>
+        <v>0.1864531373858584</v>
       </c>
       <c r="T7">
-        <v>0.9725860228737643</v>
+        <v>0.9806959205817791</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>44.99930063293049</v>
+        <v>37.49941719410874</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1776048991427069</v>
+        <v>0.1772351718005163</v>
       </c>
       <c r="C8">
-        <v>508.0520686557637</v>
+        <v>504.3508530052778</v>
       </c>
       <c r="D8">
-        <v>465.6180686557636</v>
+        <v>466.9278530052778</v>
       </c>
       <c r="E8">
-        <v>-143.934</v>
+        <v>-138.923</v>
       </c>
       <c r="F8">
-        <v>30.066</v>
+        <v>35.077</v>
       </c>
       <c r="G8">
         <v>72.5</v>
@@ -1943,28 +1943,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M8">
-        <v>1.5123198</v>
+        <v>1.7643731</v>
       </c>
       <c r="N8">
-        <v>55.1987913111111</v>
+        <v>54.9467380111111</v>
       </c>
       <c r="O8">
-        <v>12.419728045</v>
+        <v>12.3630160525</v>
       </c>
       <c r="P8">
-        <v>42.7790632661111</v>
+        <v>42.58372195861111</v>
       </c>
       <c r="Q8">
-        <v>64.1790632661111</v>
+        <v>63.98372195861111</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1864531373858584</v>
+        <v>0.1876412868822755</v>
       </c>
       <c r="T8">
-        <v>0.9806959205817791</v>
+        <v>0.9889802246921169</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>37.49941719410875</v>
+        <v>32.14235759495035</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1772351718005162</v>
+        <v>0.1768654444583256</v>
       </c>
       <c r="C9">
-        <v>504.3508530052779</v>
+        <v>500.6570269926696</v>
       </c>
       <c r="D9">
-        <v>466.9278530052779</v>
+        <v>468.2450269926696</v>
       </c>
       <c r="E9">
-        <v>-138.923</v>
+        <v>-133.912</v>
       </c>
       <c r="F9">
-        <v>35.07700000000001</v>
+        <v>40.088</v>
       </c>
       <c r="G9">
         <v>72.5</v>
@@ -2025,28 +2025,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M9">
-        <v>1.7643731</v>
+        <v>2.0164264</v>
       </c>
       <c r="N9">
-        <v>54.9467380111111</v>
+        <v>54.6946847111111</v>
       </c>
       <c r="O9">
-        <v>12.3630160525</v>
+        <v>12.30630406</v>
       </c>
       <c r="P9">
-        <v>42.58372195861111</v>
+        <v>42.38838065111111</v>
       </c>
       <c r="Q9">
-        <v>63.98372195861111</v>
+        <v>63.7883806511111</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1876412868822755</v>
+        <v>0.1888552657155713</v>
       </c>
       <c r="T9">
-        <v>0.9889802246921169</v>
+        <v>0.9974446223700706</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>32.14235759495035</v>
+        <v>28.12456289558156</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1768654444583256</v>
+        <v>0.1764957171161349</v>
       </c>
       <c r="C10">
-        <v>500.6570269926696</v>
+        <v>496.9706533319563</v>
       </c>
       <c r="D10">
-        <v>468.2450269926696</v>
+        <v>469.5696533319562</v>
       </c>
       <c r="E10">
-        <v>-133.912</v>
+        <v>-128.901</v>
       </c>
       <c r="F10">
-        <v>40.088</v>
+        <v>45.099</v>
       </c>
       <c r="G10">
         <v>72.5</v>
@@ -2107,28 +2107,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M10">
-        <v>2.0164264</v>
+        <v>2.2684797</v>
       </c>
       <c r="N10">
-        <v>54.6946847111111</v>
+        <v>54.4426314111111</v>
       </c>
       <c r="O10">
-        <v>12.30630406</v>
+        <v>12.2495920675</v>
       </c>
       <c r="P10">
-        <v>42.38838065111111</v>
+        <v>42.1930393436111</v>
       </c>
       <c r="Q10">
-        <v>63.7883806511111</v>
+        <v>63.5930393436111</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1888552657155713</v>
+        <v>0.1900959254023461</v>
       </c>
       <c r="T10">
-        <v>0.9974446223700706</v>
+        <v>1.006095050766221</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>28.12456289558156</v>
+        <v>24.99961146273916</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1764957171161349</v>
+        <v>0.1761259897739443</v>
       </c>
       <c r="C11">
-        <v>496.9706533319563</v>
+        <v>493.2917954488199</v>
       </c>
       <c r="D11">
-        <v>469.5696533319562</v>
+        <v>470.90179544882</v>
       </c>
       <c r="E11">
-        <v>-128.901</v>
+        <v>-123.89</v>
       </c>
       <c r="F11">
-        <v>45.099</v>
+        <v>50.11</v>
       </c>
       <c r="G11">
         <v>72.5</v>
@@ -2189,28 +2189,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M11">
-        <v>2.2684797</v>
+        <v>2.520533</v>
       </c>
       <c r="N11">
-        <v>54.4426314111111</v>
+        <v>54.1905781111111</v>
       </c>
       <c r="O11">
-        <v>12.2495920675</v>
+        <v>12.192880075</v>
       </c>
       <c r="P11">
-        <v>42.1930393436111</v>
+        <v>41.9976980361111</v>
       </c>
       <c r="Q11">
-        <v>63.5930393436111</v>
+        <v>63.3976980361111</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1900959254023461</v>
+        <v>0.1913641553043825</v>
       </c>
       <c r="T11">
-        <v>1.006095050766221</v>
+        <v>1.014937710904508</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.99961146273916</v>
+        <v>22.49965031646525</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1761259897739443</v>
+        <v>0.1757562624317536</v>
       </c>
       <c r="C12">
-        <v>493.2917954488199</v>
+        <v>489.6205174907302</v>
       </c>
       <c r="D12">
-        <v>470.90179544882</v>
+        <v>472.2415174907302</v>
       </c>
       <c r="E12">
-        <v>-123.89</v>
+        <v>-118.879</v>
       </c>
       <c r="F12">
-        <v>50.11000000000001</v>
+        <v>55.121</v>
       </c>
       <c r="G12">
         <v>72.5</v>
@@ -2271,28 +2271,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M12">
-        <v>2.520533</v>
+        <v>2.7725863</v>
       </c>
       <c r="N12">
-        <v>54.1905781111111</v>
+        <v>53.9385248111111</v>
       </c>
       <c r="O12">
-        <v>12.192880075</v>
+        <v>12.1361680825</v>
       </c>
       <c r="P12">
-        <v>41.9976980361111</v>
+        <v>41.8023567286111</v>
       </c>
       <c r="Q12">
-        <v>63.3976980361111</v>
+        <v>63.2023567286111</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1913641553043825</v>
+        <v>0.1926608847547793</v>
       </c>
       <c r="T12">
-        <v>1.014937710904508</v>
+        <v>1.023979082506577</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>22.49965031646525</v>
+        <v>20.45422756042295</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1757562624317536</v>
+        <v>0.175386535089563</v>
       </c>
       <c r="C13">
-        <v>489.6205174907302</v>
+        <v>485.9568843372413</v>
       </c>
       <c r="D13">
-        <v>472.2415174907302</v>
+        <v>473.5888843372414</v>
       </c>
       <c r="E13">
-        <v>-118.879</v>
+        <v>-113.868</v>
       </c>
       <c r="F13">
-        <v>55.121</v>
+        <v>60.132</v>
       </c>
       <c r="G13">
         <v>72.5</v>
@@ -2353,28 +2353,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M13">
-        <v>2.7725863</v>
+        <v>3.0246396</v>
       </c>
       <c r="N13">
-        <v>53.9385248111111</v>
+        <v>53.6864715111111</v>
       </c>
       <c r="O13">
-        <v>12.1361680825</v>
+        <v>12.07945609</v>
       </c>
       <c r="P13">
-        <v>41.8023567286111</v>
+        <v>41.6070154211111</v>
       </c>
       <c r="Q13">
-        <v>63.2023567286111</v>
+        <v>63.0070154211111</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1926608847547793</v>
+        <v>0.1939870853290488</v>
       </c>
       <c r="T13">
-        <v>1.023979082506577</v>
+        <v>1.033225939826875</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>20.45422756042295</v>
+        <v>18.74970859705438</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.175386535089563</v>
+        <v>0.1750168077473723</v>
       </c>
       <c r="C14">
-        <v>485.9568843372413</v>
+        <v>482.3009616104655</v>
       </c>
       <c r="D14">
-        <v>473.5888843372414</v>
+        <v>474.9439616104656</v>
       </c>
       <c r="E14">
-        <v>-113.868</v>
+        <v>-108.857</v>
       </c>
       <c r="F14">
-        <v>60.132</v>
+        <v>65.143</v>
       </c>
       <c r="G14">
         <v>72.5</v>
@@ -2435,28 +2435,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M14">
-        <v>3.0246396</v>
+        <v>3.2766929</v>
       </c>
       <c r="N14">
-        <v>53.6864715111111</v>
+        <v>53.4344182111111</v>
       </c>
       <c r="O14">
-        <v>12.07945609</v>
+        <v>12.0227440975</v>
       </c>
       <c r="P14">
-        <v>41.6070154211111</v>
+        <v>41.4116741136111</v>
       </c>
       <c r="Q14">
-        <v>63.0070154211111</v>
+        <v>62.8116741136111</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1939870853290488</v>
+        <v>0.1953437732728417</v>
       </c>
       <c r="T14">
-        <v>1.033225939826875</v>
+        <v>1.042685368579824</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.74970859705438</v>
+        <v>17.30742332035788</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1750168077473723</v>
+        <v>0.1746470804051816</v>
       </c>
       <c r="C15">
-        <v>482.3009616104655</v>
+        <v>478.6528156857271</v>
       </c>
       <c r="D15">
-        <v>474.9439616104656</v>
+        <v>476.3068156857271</v>
       </c>
       <c r="E15">
-        <v>-108.857</v>
+        <v>-103.846</v>
       </c>
       <c r="F15">
-        <v>65.143</v>
+        <v>70.15400000000001</v>
       </c>
       <c r="G15">
         <v>72.5</v>
@@ -2517,28 +2517,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M15">
-        <v>3.2766929</v>
+        <v>3.5287462</v>
       </c>
       <c r="N15">
-        <v>53.4344182111111</v>
+        <v>53.1823649111111</v>
       </c>
       <c r="O15">
-        <v>12.0227440975</v>
+        <v>11.966032105</v>
       </c>
       <c r="P15">
-        <v>41.4116741136111</v>
+        <v>41.2163328061111</v>
       </c>
       <c r="Q15">
-        <v>62.8116741136111</v>
+        <v>62.6163328061111</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1953437732728417</v>
+        <v>0.1967320120990484</v>
       </c>
       <c r="T15">
-        <v>1.042685368579824</v>
+        <v>1.052364784047957</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>17.30742332035788</v>
+        <v>16.07117879747518</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1746470804051816</v>
+        <v>0.1742773530629909</v>
       </c>
       <c r="C16">
-        <v>478.6528156857271</v>
+        <v>475.0125137023998</v>
       </c>
       <c r="D16">
-        <v>476.3068156857271</v>
+        <v>477.6775137023998</v>
       </c>
       <c r="E16">
-        <v>-103.846</v>
+        <v>-98.83499999999998</v>
       </c>
       <c r="F16">
-        <v>70.15400000000001</v>
+        <v>75.16500000000002</v>
       </c>
       <c r="G16">
         <v>72.5</v>
@@ -2599,28 +2599,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M16">
-        <v>3.5287462</v>
+        <v>3.780799500000001</v>
       </c>
       <c r="N16">
-        <v>53.1823649111111</v>
+        <v>52.9303116111111</v>
       </c>
       <c r="O16">
-        <v>11.966032105</v>
+        <v>11.9093201125</v>
       </c>
       <c r="P16">
-        <v>41.2163328061111</v>
+        <v>41.0209914986111</v>
       </c>
       <c r="Q16">
-        <v>62.6163328061111</v>
+        <v>62.4209914986111</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1967320120990484</v>
+        <v>0.1981529153682246</v>
       </c>
       <c r="T16">
-        <v>1.052364784047957</v>
+        <v>1.062271950468281</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>16.07117879747518</v>
+        <v>14.99976687764349</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1742773530629909</v>
+        <v>0.1739076257208003</v>
       </c>
       <c r="C17">
-        <v>475.0125137023998</v>
+        <v>471.3801235749326</v>
       </c>
       <c r="D17">
-        <v>477.6775137023998</v>
+        <v>479.0561235749325</v>
       </c>
       <c r="E17">
-        <v>-98.83499999999999</v>
+        <v>-93.824</v>
       </c>
       <c r="F17">
-        <v>75.16500000000001</v>
+        <v>80.176</v>
       </c>
       <c r="G17">
         <v>72.5</v>
@@ -2681,28 +2681,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M17">
-        <v>3.7807995</v>
+        <v>4.0328528</v>
       </c>
       <c r="N17">
-        <v>52.9303116111111</v>
+        <v>52.6782583111111</v>
       </c>
       <c r="O17">
-        <v>11.9093201125</v>
+        <v>11.85260812</v>
       </c>
       <c r="P17">
-        <v>41.0209914986111</v>
+        <v>40.8256501911111</v>
       </c>
       <c r="Q17">
-        <v>62.4209914986111</v>
+        <v>62.2256501911111</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1981529153682246</v>
+        <v>0.1996076496676194</v>
       </c>
       <c r="T17">
-        <v>1.062271950468281</v>
+        <v>1.072415001803375</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.9997668776435</v>
+        <v>14.06228144779078</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1739076257208003</v>
+        <v>0.1735378983786096</v>
       </c>
       <c r="C18">
-        <v>471.3801235749326</v>
+        <v>467.7557140040668</v>
       </c>
       <c r="D18">
-        <v>479.0561235749325</v>
+        <v>480.4427140040668</v>
       </c>
       <c r="E18">
-        <v>-93.824</v>
+        <v>-88.81299999999999</v>
       </c>
       <c r="F18">
-        <v>80.176</v>
+        <v>85.18700000000001</v>
       </c>
       <c r="G18">
         <v>72.5</v>
@@ -2763,28 +2763,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M18">
-        <v>4.0328528</v>
+        <v>4.284906100000001</v>
       </c>
       <c r="N18">
-        <v>52.6782583111111</v>
+        <v>52.4262050111111</v>
       </c>
       <c r="O18">
-        <v>11.85260812</v>
+        <v>11.7958961275</v>
       </c>
       <c r="P18">
-        <v>40.8256501911111</v>
+        <v>40.63030888361111</v>
       </c>
       <c r="Q18">
-        <v>62.2256501911111</v>
+        <v>62.03030888361111</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1996076496676194</v>
+        <v>0.2010974378055538</v>
       </c>
       <c r="T18">
-        <v>1.072415001803375</v>
+        <v>1.082802464014014</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>14.06228144779078</v>
+        <v>13.23508842145014</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1735378983786096</v>
+        <v>0.1733774210364189</v>
       </c>
       <c r="C19">
-        <v>467.7557140040668</v>
+        <v>463.3490542485388</v>
       </c>
       <c r="D19">
-        <v>480.4427140040668</v>
+        <v>481.0470542485388</v>
       </c>
       <c r="E19">
-        <v>-88.81299999999999</v>
+        <v>-83.80199999999998</v>
       </c>
       <c r="F19">
-        <v>85.18700000000001</v>
+        <v>90.19800000000002</v>
       </c>
       <c r="G19">
         <v>72.5</v>
@@ -2845,45 +2845,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M19">
-        <v>4.284906100000001</v>
+        <v>4.672256400000001</v>
       </c>
       <c r="N19">
-        <v>52.4262050111111</v>
+        <v>52.0388547111111</v>
       </c>
       <c r="O19">
-        <v>11.7958961275</v>
+        <v>11.70874231</v>
       </c>
       <c r="P19">
-        <v>40.63030888361111</v>
+        <v>40.3301124011111</v>
       </c>
       <c r="Q19">
-        <v>62.03030888361111</v>
+        <v>61.7301124011111</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2010974378055538</v>
+        <v>0.2026235622395353</v>
       </c>
       <c r="T19">
-        <v>1.082802464014014</v>
+        <v>1.093443278961497</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.225</v>
       </c>
       <c r="W19">
-        <v>0.0389825</v>
+        <v>0.040145</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>13.23508842145014</v>
+        <v>12.13784224493996</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.173377421036419</v>
+        <v>0.1730193186942283</v>
       </c>
       <c r="C20">
-        <v>463.3490542485388</v>
+        <v>459.6921259304062</v>
       </c>
       <c r="D20">
-        <v>481.0470542485388</v>
+        <v>482.4011259304062</v>
       </c>
       <c r="E20">
-        <v>-83.80199999999999</v>
+        <v>-78.791</v>
       </c>
       <c r="F20">
-        <v>90.19800000000001</v>
+        <v>95.209</v>
       </c>
       <c r="G20">
         <v>72.5</v>
@@ -2927,28 +2927,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M20">
-        <v>4.6722564</v>
+        <v>4.9318262</v>
       </c>
       <c r="N20">
-        <v>52.0388547111111</v>
+        <v>51.77928491111111</v>
       </c>
       <c r="O20">
-        <v>11.70874231</v>
+        <v>11.650339105</v>
       </c>
       <c r="P20">
-        <v>40.3301124011111</v>
+        <v>40.1289458061111</v>
       </c>
       <c r="Q20">
-        <v>61.7301124011111</v>
+        <v>61.5289458061111</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2026235622395353</v>
+        <v>0.2041873687583065</v>
       </c>
       <c r="T20">
-        <v>1.093443278961497</v>
+        <v>1.104346830080523</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>12.13784224493996</v>
+        <v>11.4990084425747</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1730193186942283</v>
+        <v>0.1726612163520376</v>
       </c>
       <c r="C21">
-        <v>459.6921259304062</v>
+        <v>456.0428421273541</v>
       </c>
       <c r="D21">
-        <v>482.4011259304062</v>
+        <v>483.7628421273542</v>
       </c>
       <c r="E21">
-        <v>-78.791</v>
+        <v>-73.77999999999999</v>
       </c>
       <c r="F21">
-        <v>95.209</v>
+        <v>100.22</v>
       </c>
       <c r="G21">
         <v>72.5</v>
@@ -3009,28 +3009,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M21">
-        <v>4.9318262</v>
+        <v>5.191396</v>
       </c>
       <c r="N21">
-        <v>51.77928491111111</v>
+        <v>51.5197151111111</v>
       </c>
       <c r="O21">
-        <v>11.650339105</v>
+        <v>11.5919359</v>
       </c>
       <c r="P21">
-        <v>40.1289458061111</v>
+        <v>39.9277792111111</v>
       </c>
       <c r="Q21">
-        <v>61.5289458061111</v>
+        <v>61.3277792111111</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2041873687583065</v>
+        <v>0.205790270440047</v>
       </c>
       <c r="T21">
-        <v>1.104346830080523</v>
+        <v>1.115522969977526</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.4990084425747</v>
+        <v>10.92405802044597</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1726612163520376</v>
+        <v>0.172303114009847</v>
       </c>
       <c r="C22">
-        <v>456.0428421273541</v>
+        <v>452.4012677591779</v>
       </c>
       <c r="D22">
-        <v>483.7628421273542</v>
+        <v>485.1322677591779</v>
       </c>
       <c r="E22">
-        <v>-73.77999999999999</v>
+        <v>-68.76899999999999</v>
       </c>
       <c r="F22">
-        <v>100.22</v>
+        <v>105.231</v>
       </c>
       <c r="G22">
         <v>72.5</v>
@@ -3091,28 +3091,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M22">
-        <v>5.191396</v>
+        <v>5.450965800000001</v>
       </c>
       <c r="N22">
-        <v>51.5197151111111</v>
+        <v>51.2601453111111</v>
       </c>
       <c r="O22">
-        <v>11.5919359</v>
+        <v>11.533532695</v>
       </c>
       <c r="P22">
-        <v>39.9277792111111</v>
+        <v>39.7266126161111</v>
       </c>
       <c r="Q22">
-        <v>61.3277792111111</v>
+        <v>61.1266126161111</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.205790270440047</v>
+        <v>0.2074337519111987</v>
       </c>
       <c r="T22">
-        <v>1.115522969977526</v>
+        <v>1.126982050125084</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.92405802044597</v>
+        <v>10.40386478137711</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.172303114009847</v>
+        <v>0.1719450116676563</v>
       </c>
       <c r="C23">
-        <v>452.4012677591779</v>
+        <v>448.767468482854</v>
       </c>
       <c r="D23">
-        <v>485.1322677591779</v>
+        <v>486.509468482854</v>
       </c>
       <c r="E23">
-        <v>-68.76900000000001</v>
+        <v>-63.758</v>
       </c>
       <c r="F23">
-        <v>105.231</v>
+        <v>110.242</v>
       </c>
       <c r="G23">
         <v>72.5</v>
@@ -3173,28 +3173,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M23">
-        <v>5.4509658</v>
+        <v>5.7105356</v>
       </c>
       <c r="N23">
-        <v>51.2601453111111</v>
+        <v>51.0005755111111</v>
       </c>
       <c r="O23">
-        <v>11.533532695</v>
+        <v>11.47512949</v>
       </c>
       <c r="P23">
-        <v>39.7266126161111</v>
+        <v>39.5254460211111</v>
       </c>
       <c r="Q23">
-        <v>61.1266126161111</v>
+        <v>60.9254460211111</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2074337519111987</v>
+        <v>0.2091193739328927</v>
       </c>
       <c r="T23">
-        <v>1.126982050125084</v>
+        <v>1.13873495284053</v>
       </c>
       <c r="U23">
         <v>0.0518</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>10.40386478137711</v>
+        <v>9.930961836769059</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1719450116676563</v>
+        <v>0.1718899343254656</v>
       </c>
       <c r="C24">
-        <v>448.767468482854</v>
+        <v>443.9689806759802</v>
       </c>
       <c r="D24">
-        <v>486.509468482854</v>
+        <v>486.7219806759803</v>
       </c>
       <c r="E24">
-        <v>-63.758</v>
+        <v>-58.74699999999999</v>
       </c>
       <c r="F24">
-        <v>110.242</v>
+        <v>115.253</v>
       </c>
       <c r="G24">
         <v>72.5</v>
@@ -3255,45 +3255,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M24">
-        <v>5.7105356</v>
+        <v>6.1660355</v>
       </c>
       <c r="N24">
-        <v>51.0005755111111</v>
+        <v>50.5450756111111</v>
       </c>
       <c r="O24">
-        <v>11.47512949</v>
+        <v>11.3726420125</v>
       </c>
       <c r="P24">
-        <v>39.5254460211111</v>
+        <v>39.17243359861111</v>
       </c>
       <c r="Q24">
-        <v>60.9254460211111</v>
+        <v>60.57243359861111</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.2091193739328927</v>
+        <v>0.2108487783447605</v>
       </c>
       <c r="T24">
-        <v>1.13873495284053</v>
+        <v>1.150793125756376</v>
       </c>
       <c r="U24">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V24">
         <v>0.225</v>
       </c>
       <c r="W24">
-        <v>0.040145</v>
+        <v>0.0414625</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>9.930961836769059</v>
+        <v>9.197337756344591</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1718899343254656</v>
+        <v>0.1715450069832749</v>
       </c>
       <c r="C25">
-        <v>443.9689806759802</v>
+        <v>440.2930930848783</v>
       </c>
       <c r="D25">
-        <v>486.7219806759803</v>
+        <v>488.0570930848783</v>
       </c>
       <c r="E25">
-        <v>-58.74699999999999</v>
+        <v>-53.73599999999999</v>
       </c>
       <c r="F25">
-        <v>115.253</v>
+        <v>120.264</v>
       </c>
       <c r="G25">
         <v>72.5</v>
@@ -3337,28 +3337,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M25">
-        <v>6.1660355</v>
+        <v>6.434124000000001</v>
       </c>
       <c r="N25">
-        <v>50.5450756111111</v>
+        <v>50.2769871111111</v>
       </c>
       <c r="O25">
-        <v>11.3726420125</v>
+        <v>11.3123221</v>
       </c>
       <c r="P25">
-        <v>39.17243359861111</v>
+        <v>38.9646650111111</v>
       </c>
       <c r="Q25">
-        <v>60.57243359861111</v>
+        <v>60.3646650111111</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2108487783447605</v>
+        <v>0.212623693399046</v>
       </c>
       <c r="T25">
-        <v>1.150793125756376</v>
+        <v>1.163168619012113</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>9.197337756344591</v>
+        <v>8.814115349830232</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1715450069832749</v>
+        <v>0.1712000796410843</v>
       </c>
       <c r="C26">
-        <v>440.2930930848783</v>
+        <v>436.6245502542589</v>
       </c>
       <c r="D26">
-        <v>488.0570930848783</v>
+        <v>489.3995502542589</v>
       </c>
       <c r="E26">
-        <v>-53.736</v>
+        <v>-48.72499999999999</v>
       </c>
       <c r="F26">
-        <v>120.264</v>
+        <v>125.275</v>
       </c>
       <c r="G26">
         <v>72.5</v>
@@ -3419,28 +3419,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M26">
-        <v>6.434124</v>
+        <v>6.7022125</v>
       </c>
       <c r="N26">
-        <v>50.2769871111111</v>
+        <v>50.0088986111111</v>
       </c>
       <c r="O26">
-        <v>11.3123221</v>
+        <v>11.2520021875</v>
       </c>
       <c r="P26">
-        <v>38.96466501111111</v>
+        <v>38.7568964236111</v>
       </c>
       <c r="Q26">
-        <v>60.36466501111111</v>
+        <v>60.1568964236111</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.212623693399046</v>
+        <v>0.2144459395214457</v>
       </c>
       <c r="T26">
-        <v>1.163168619012113</v>
+        <v>1.175874125421336</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.814115349830235</v>
+        <v>8.461550735837024</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1712000796410843</v>
+        <v>0.1708551522988936</v>
       </c>
       <c r="C27">
-        <v>436.6245502542589</v>
+        <v>432.9634129591159</v>
       </c>
       <c r="D27">
-        <v>489.3995502542589</v>
+        <v>490.7494129591159</v>
       </c>
       <c r="E27">
-        <v>-48.72499999999999</v>
+        <v>-43.714</v>
       </c>
       <c r="F27">
-        <v>125.275</v>
+        <v>130.286</v>
       </c>
       <c r="G27">
         <v>72.5</v>
@@ -3501,28 +3501,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M27">
-        <v>6.7022125</v>
+        <v>6.970301</v>
       </c>
       <c r="N27">
-        <v>50.0088986111111</v>
+        <v>49.7408101111111</v>
       </c>
       <c r="O27">
-        <v>11.2520021875</v>
+        <v>11.191682275</v>
       </c>
       <c r="P27">
-        <v>38.7568964236111</v>
+        <v>38.5491278361111</v>
       </c>
       <c r="Q27">
-        <v>60.1568964236111</v>
+        <v>59.9491278361111</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2144459395214457</v>
+        <v>0.2163174355390455</v>
       </c>
       <c r="T27">
-        <v>1.175874125421336</v>
+        <v>1.188923023895673</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.461550735837024</v>
+        <v>8.136106476766368</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1708551522988936</v>
+        <v>0.170510224956703</v>
       </c>
       <c r="C28">
-        <v>432.9634129591159</v>
+        <v>429.309742646817</v>
       </c>
       <c r="D28">
-        <v>490.7494129591159</v>
+        <v>492.106742646817</v>
       </c>
       <c r="E28">
-        <v>-43.714</v>
+        <v>-38.70299999999997</v>
       </c>
       <c r="F28">
-        <v>130.286</v>
+        <v>135.297</v>
       </c>
       <c r="G28">
         <v>72.5</v>
@@ -3583,28 +3583,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M28">
-        <v>6.970301</v>
+        <v>7.238389500000001</v>
       </c>
       <c r="N28">
-        <v>49.7408101111111</v>
+        <v>49.4727216111111</v>
       </c>
       <c r="O28">
-        <v>11.191682275</v>
+        <v>11.1313623625</v>
       </c>
       <c r="P28">
-        <v>38.5491278361111</v>
+        <v>38.3413592486111</v>
       </c>
       <c r="Q28">
-        <v>59.9491278361111</v>
+        <v>59.7413592486111</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2163174355390455</v>
+        <v>0.2182402054201411</v>
       </c>
       <c r="T28">
-        <v>1.188923023895673</v>
+        <v>1.202329426437801</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>8.136106476766368</v>
+        <v>7.834769199849095</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.170510224956703</v>
+        <v>0.1703388976145123</v>
       </c>
       <c r="C29">
-        <v>429.309742646817</v>
+        <v>424.9757306554372</v>
       </c>
       <c r="D29">
-        <v>492.106742646817</v>
+        <v>492.7837306554372</v>
       </c>
       <c r="E29">
-        <v>-38.70299999999997</v>
+        <v>-33.69199999999998</v>
       </c>
       <c r="F29">
-        <v>135.297</v>
+        <v>140.308</v>
       </c>
       <c r="G29">
         <v>72.5</v>
@@ -3665,45 +3665,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M29">
-        <v>7.238389500000001</v>
+        <v>7.618724400000001</v>
       </c>
       <c r="N29">
-        <v>49.4727216111111</v>
+        <v>49.0923867111111</v>
       </c>
       <c r="O29">
-        <v>11.1313623625</v>
+        <v>11.04578701</v>
       </c>
       <c r="P29">
-        <v>38.3413592486111</v>
+        <v>38.04659970111111</v>
       </c>
       <c r="Q29">
-        <v>59.7413592486111</v>
+        <v>59.4465997011111</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2182402054201411</v>
+        <v>0.2202163855757115</v>
       </c>
       <c r="T29">
-        <v>1.202329426437801</v>
+        <v>1.216108229050543</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.225</v>
       </c>
       <c r="W29">
-        <v>0.0414625</v>
+        <v>0.0420825</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.834769199849095</v>
+        <v>7.443649111537765</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1703388976145123</v>
+        <v>0.1700001702723216</v>
       </c>
       <c r="C30">
-        <v>424.9757306554372</v>
+        <v>421.3086847176073</v>
       </c>
       <c r="D30">
-        <v>492.7837306554372</v>
+        <v>494.1276847176073</v>
       </c>
       <c r="E30">
-        <v>-33.69199999999998</v>
+        <v>-28.68099999999998</v>
       </c>
       <c r="F30">
-        <v>140.308</v>
+        <v>145.319</v>
       </c>
       <c r="G30">
         <v>72.5</v>
@@ -3747,28 +3747,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M30">
-        <v>7.618724400000001</v>
+        <v>7.890821700000001</v>
       </c>
       <c r="N30">
-        <v>49.0923867111111</v>
+        <v>48.8202894111111</v>
       </c>
       <c r="O30">
-        <v>11.04578701</v>
+        <v>10.9845651175</v>
       </c>
       <c r="P30">
-        <v>38.04659970111111</v>
+        <v>37.8357242936111</v>
       </c>
       <c r="Q30">
-        <v>59.4465997011111</v>
+        <v>59.2357242936111</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2202163855757115</v>
+        <v>0.2222482327779178</v>
       </c>
       <c r="T30">
-        <v>1.216108229050543</v>
+        <v>1.230275166948151</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.443649111537765</v>
+        <v>7.186971555967498</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1700001702723216</v>
+        <v>0.169661442930131</v>
       </c>
       <c r="C31">
-        <v>421.3086847176075</v>
+        <v>417.6489894770847</v>
       </c>
       <c r="D31">
-        <v>494.1276847176075</v>
+        <v>495.4789894770848</v>
       </c>
       <c r="E31">
-        <v>-28.68100000000001</v>
+        <v>-23.66999999999999</v>
       </c>
       <c r="F31">
-        <v>145.319</v>
+        <v>150.33</v>
       </c>
       <c r="G31">
         <v>72.5</v>
@@ -3829,28 +3829,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M31">
-        <v>7.890821699999999</v>
+        <v>8.162919</v>
       </c>
       <c r="N31">
-        <v>48.8202894111111</v>
+        <v>48.5481921111111</v>
       </c>
       <c r="O31">
-        <v>10.9845651175</v>
+        <v>10.923343225</v>
       </c>
       <c r="P31">
-        <v>37.83572429361111</v>
+        <v>37.6248488861111</v>
       </c>
       <c r="Q31">
-        <v>59.23572429361111</v>
+        <v>59.0248488861111</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.2222482327779178</v>
+        <v>0.22433813275733</v>
       </c>
       <c r="T31">
-        <v>1.230275166948151</v>
+        <v>1.244846874499976</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.186971555967499</v>
+        <v>6.947405837435248</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.169661442930131</v>
+        <v>0.1693227155879403</v>
       </c>
       <c r="C32">
-        <v>417.6489894770847</v>
+        <v>413.9967054057141</v>
       </c>
       <c r="D32">
-        <v>495.4789894770848</v>
+        <v>496.8377054057141</v>
       </c>
       <c r="E32">
-        <v>-23.66999999999999</v>
+        <v>-18.65899999999999</v>
       </c>
       <c r="F32">
-        <v>150.33</v>
+        <v>155.341</v>
       </c>
       <c r="G32">
         <v>72.5</v>
@@ -3911,28 +3911,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M32">
-        <v>8.162919</v>
+        <v>8.435016300000001</v>
       </c>
       <c r="N32">
-        <v>48.5481921111111</v>
+        <v>48.2760948111111</v>
       </c>
       <c r="O32">
-        <v>10.923343225</v>
+        <v>10.8621213325</v>
       </c>
       <c r="P32">
-        <v>37.6248488861111</v>
+        <v>37.4139734786111</v>
       </c>
       <c r="Q32">
-        <v>59.0248488861111</v>
+        <v>58.8139734786111</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.22433813275733</v>
+        <v>0.2264886095477396</v>
       </c>
       <c r="T32">
-        <v>1.244846874499976</v>
+        <v>1.259840950386637</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.947405837435248</v>
+        <v>6.72329597171153</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1693227155879403</v>
+        <v>0.1689839882457496</v>
       </c>
       <c r="C33">
-        <v>413.9967054057141</v>
+        <v>410.3518936404745</v>
       </c>
       <c r="D33">
-        <v>496.8377054057141</v>
+        <v>498.2038936404745</v>
       </c>
       <c r="E33">
-        <v>-18.65899999999999</v>
+        <v>-13.648</v>
       </c>
       <c r="F33">
-        <v>155.341</v>
+        <v>160.352</v>
       </c>
       <c r="G33">
         <v>72.5</v>
@@ -3993,28 +3993,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M33">
-        <v>8.435016300000001</v>
+        <v>8.7071136</v>
       </c>
       <c r="N33">
-        <v>48.2760948111111</v>
+        <v>48.0039975111111</v>
       </c>
       <c r="O33">
-        <v>10.8621213325</v>
+        <v>10.80089944</v>
       </c>
       <c r="P33">
-        <v>37.4139734786111</v>
+        <v>37.2030980711111</v>
       </c>
       <c r="Q33">
-        <v>58.8139734786111</v>
+        <v>58.6030980711111</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2264886095477396</v>
+        <v>0.2287023356555142</v>
       </c>
       <c r="T33">
-        <v>1.259840950386637</v>
+        <v>1.275276028505259</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.72329597171153</v>
+        <v>6.513192972595546</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1689839882457496</v>
+        <v>0.168645260903559</v>
       </c>
       <c r="C34">
-        <v>410.3518936404745</v>
+        <v>406.7146159926484</v>
       </c>
       <c r="D34">
-        <v>498.2038936404745</v>
+        <v>499.5776159926485</v>
       </c>
       <c r="E34">
-        <v>-13.648</v>
+        <v>-8.636999999999972</v>
       </c>
       <c r="F34">
-        <v>160.352</v>
+        <v>165.363</v>
       </c>
       <c r="G34">
         <v>72.5</v>
@@ -4075,28 +4075,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M34">
-        <v>8.7071136</v>
+        <v>8.979210900000002</v>
       </c>
       <c r="N34">
-        <v>48.0039975111111</v>
+        <v>47.7319002111111</v>
       </c>
       <c r="O34">
-        <v>10.80089944</v>
+        <v>10.7396775475</v>
       </c>
       <c r="P34">
-        <v>37.2030980711111</v>
+        <v>36.9922226636111</v>
       </c>
       <c r="Q34">
-        <v>58.6030980711111</v>
+        <v>58.3922226636111</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2287023356555142</v>
+        <v>0.2309821431396403</v>
       </c>
       <c r="T34">
-        <v>1.275276028505259</v>
+        <v>1.291171855224436</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.513192972595546</v>
+        <v>6.315823488577497</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.168645260903559</v>
+        <v>0.1683065335613683</v>
       </c>
       <c r="C35">
-        <v>406.7146159926484</v>
+        <v>403.0849349571458</v>
       </c>
       <c r="D35">
-        <v>499.5776159926485</v>
+        <v>500.9589349571458</v>
       </c>
       <c r="E35">
-        <v>-8.636999999999972</v>
+        <v>-3.625999999999976</v>
       </c>
       <c r="F35">
-        <v>165.363</v>
+        <v>170.374</v>
       </c>
       <c r="G35">
         <v>72.5</v>
@@ -4157,28 +4157,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M35">
-        <v>8.979210900000002</v>
+        <v>9.251308200000002</v>
       </c>
       <c r="N35">
-        <v>47.7319002111111</v>
+        <v>47.4598029111111</v>
       </c>
       <c r="O35">
-        <v>10.7396775475</v>
+        <v>10.678455655</v>
       </c>
       <c r="P35">
-        <v>36.9922226636111</v>
+        <v>36.7813472561111</v>
       </c>
       <c r="Q35">
-        <v>58.3922226636111</v>
+        <v>58.1813472561111</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2309821431396403</v>
+        <v>0.2333310356990429</v>
       </c>
       <c r="T35">
-        <v>1.291171855224436</v>
+        <v>1.307549373662377</v>
       </c>
       <c r="U35">
         <v>0.0543</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>6.315823488577497</v>
+        <v>6.13006397420757</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1683065335613683</v>
+        <v>0.1682390562191776</v>
       </c>
       <c r="C36">
-        <v>403.0849349571458</v>
+        <v>398.3500182472444</v>
       </c>
       <c r="D36">
-        <v>500.9589349571458</v>
+        <v>501.2350182472444</v>
       </c>
       <c r="E36">
-        <v>-3.625999999999976</v>
+        <v>1.385000000000019</v>
       </c>
       <c r="F36">
-        <v>170.374</v>
+        <v>175.385</v>
       </c>
       <c r="G36">
         <v>72.5</v>
@@ -4239,45 +4239,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M36">
-        <v>9.251308200000002</v>
+        <v>9.698790500000001</v>
       </c>
       <c r="N36">
-        <v>47.4598029111111</v>
+        <v>47.0123206111111</v>
       </c>
       <c r="O36">
-        <v>10.678455655</v>
+        <v>10.5777721375</v>
       </c>
       <c r="P36">
-        <v>36.7813472561111</v>
+        <v>36.4345484736111</v>
       </c>
       <c r="Q36">
-        <v>58.1813472561111</v>
+        <v>57.8345484736111</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2333310356990429</v>
+        <v>0.2357522018756579</v>
       </c>
       <c r="T36">
-        <v>1.307549373662377</v>
+        <v>1.324430815744561</v>
       </c>
       <c r="U36">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V36">
         <v>0.225</v>
       </c>
       <c r="W36">
-        <v>0.0420825</v>
+        <v>0.0428575</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y36">
-        <v>6.13006397420757</v>
+        <v>5.847235396115742</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1682390562191776</v>
+        <v>0.1679080788769869</v>
       </c>
       <c r="C37">
-        <v>398.3500182472444</v>
+        <v>394.6976296976751</v>
       </c>
       <c r="D37">
-        <v>501.2350182472444</v>
+        <v>502.5936296976752</v>
       </c>
       <c r="E37">
-        <v>1.385000000000019</v>
+        <v>6.396000000000043</v>
       </c>
       <c r="F37">
-        <v>175.385</v>
+        <v>180.396</v>
       </c>
       <c r="G37">
         <v>72.5</v>
@@ -4321,28 +4321,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M37">
-        <v>9.698790500000001</v>
+        <v>9.975898800000003</v>
       </c>
       <c r="N37">
-        <v>47.0123206111111</v>
+        <v>46.7352123111111</v>
       </c>
       <c r="O37">
-        <v>10.5777721375</v>
+        <v>10.51542277</v>
       </c>
       <c r="P37">
-        <v>36.4345484736111</v>
+        <v>36.2197895411111</v>
       </c>
       <c r="Q37">
-        <v>57.8345484736111</v>
+        <v>57.6197895411111</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2357522018756579</v>
+        <v>0.2382490294952922</v>
       </c>
       <c r="T37">
-        <v>1.324430815744561</v>
+        <v>1.341839802891814</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.847235396115742</v>
+        <v>5.684812190668081</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.167908078876987</v>
+        <v>0.1675771015347963</v>
       </c>
       <c r="C38">
-        <v>394.6976296976752</v>
+        <v>391.0526262739014</v>
       </c>
       <c r="D38">
-        <v>502.5936296976751</v>
+        <v>503.9596262739014</v>
       </c>
       <c r="E38">
-        <v>6.396000000000015</v>
+        <v>11.40700000000001</v>
       </c>
       <c r="F38">
-        <v>180.396</v>
+        <v>185.407</v>
       </c>
       <c r="G38">
         <v>72.5</v>
@@ -4403,28 +4403,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M38">
-        <v>9.975898800000001</v>
+        <v>10.2530071</v>
       </c>
       <c r="N38">
-        <v>46.7352123111111</v>
+        <v>46.4581040111111</v>
       </c>
       <c r="O38">
-        <v>10.51542277</v>
+        <v>10.4530734025</v>
       </c>
       <c r="P38">
-        <v>36.2197895411111</v>
+        <v>36.00503060861111</v>
       </c>
       <c r="Q38">
-        <v>57.6197895411111</v>
+        <v>57.40503060861111</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2382490294952922</v>
+        <v>0.2408251214838037</v>
       </c>
       <c r="T38">
-        <v>1.341839802891814</v>
+        <v>1.35980145629771</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.684812190668082</v>
+        <v>5.531168617947324</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1675771015347963</v>
+        <v>0.1672461241926056</v>
       </c>
       <c r="C39">
-        <v>391.0526262739014</v>
+        <v>387.4150683560134</v>
       </c>
       <c r="D39">
-        <v>503.9596262739014</v>
+        <v>505.3330683560135</v>
       </c>
       <c r="E39">
-        <v>11.40700000000001</v>
+        <v>16.41800000000001</v>
       </c>
       <c r="F39">
-        <v>185.407</v>
+        <v>190.418</v>
       </c>
       <c r="G39">
         <v>72.5</v>
@@ -4485,28 +4485,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M39">
-        <v>10.2530071</v>
+        <v>10.5301154</v>
       </c>
       <c r="N39">
-        <v>46.4581040111111</v>
+        <v>46.1809957111111</v>
       </c>
       <c r="O39">
-        <v>10.4530734025</v>
+        <v>10.390724035</v>
       </c>
       <c r="P39">
-        <v>36.00503060861111</v>
+        <v>35.7902716761111</v>
       </c>
       <c r="Q39">
-        <v>57.40503060861111</v>
+        <v>57.1902716761111</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2408251214838037</v>
+        <v>0.2434843132138801</v>
       </c>
       <c r="T39">
-        <v>1.35980145629771</v>
+        <v>1.37834251787799</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.531168617947324</v>
+        <v>5.385611549053973</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1672461241926056</v>
+        <v>0.166915146850415</v>
       </c>
       <c r="C40">
-        <v>387.4150683560134</v>
+        <v>383.7850169841162</v>
       </c>
       <c r="D40">
-        <v>505.3330683560135</v>
+        <v>506.7140169841161</v>
       </c>
       <c r="E40">
-        <v>16.41800000000001</v>
+        <v>21.429</v>
       </c>
       <c r="F40">
-        <v>190.418</v>
+        <v>195.429</v>
       </c>
       <c r="G40">
         <v>72.5</v>
@@ -4567,28 +4567,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M40">
-        <v>10.5301154</v>
+        <v>10.8072237</v>
       </c>
       <c r="N40">
-        <v>46.1809957111111</v>
+        <v>45.9038874111111</v>
       </c>
       <c r="O40">
-        <v>10.390724035</v>
+        <v>10.3283746675</v>
       </c>
       <c r="P40">
-        <v>35.7902716761111</v>
+        <v>35.5755127436111</v>
       </c>
       <c r="Q40">
-        <v>57.1902716761111</v>
+        <v>56.9755127436111</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2434843132138801</v>
+        <v>0.2462306915580574</v>
       </c>
       <c r="T40">
-        <v>1.37834251787799</v>
+        <v>1.397491483116639</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.385611549053973</v>
+        <v>5.247518945232077</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.166915146850415</v>
+        <v>0.1665841695082243</v>
       </c>
       <c r="C41">
-        <v>383.7850169841162</v>
+        <v>380.1625338673716</v>
       </c>
       <c r="D41">
-        <v>506.7140169841161</v>
+        <v>508.1025338673717</v>
       </c>
       <c r="E41">
-        <v>21.429</v>
+        <v>26.44000000000003</v>
       </c>
       <c r="F41">
-        <v>195.429</v>
+        <v>200.44</v>
       </c>
       <c r="G41">
         <v>72.5</v>
@@ -4649,28 +4649,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M41">
-        <v>10.8072237</v>
+        <v>11.084332</v>
       </c>
       <c r="N41">
-        <v>45.9038874111111</v>
+        <v>45.6267791111111</v>
       </c>
       <c r="O41">
-        <v>10.3283746675</v>
+        <v>10.2660253</v>
       </c>
       <c r="P41">
-        <v>35.5755127436111</v>
+        <v>35.3607538111111</v>
       </c>
       <c r="Q41">
-        <v>56.9755127436111</v>
+        <v>56.7607538111111</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2462306915580574</v>
+        <v>0.2490686158470405</v>
       </c>
       <c r="T41">
-        <v>1.397491483116639</v>
+        <v>1.417278747196577</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.247518945232077</v>
+        <v>5.116330971601274</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1665841695082243</v>
+        <v>0.1662531921660337</v>
       </c>
       <c r="C42">
-        <v>380.1625338673716</v>
+        <v>376.5476813931919</v>
       </c>
       <c r="D42">
-        <v>508.1025338673717</v>
+        <v>509.4986813931919</v>
       </c>
       <c r="E42">
-        <v>26.44000000000003</v>
+        <v>31.45100000000002</v>
       </c>
       <c r="F42">
-        <v>200.44</v>
+        <v>205.451</v>
       </c>
       <c r="G42">
         <v>72.5</v>
@@ -4731,28 +4731,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M42">
-        <v>11.084332</v>
+        <v>11.3614403</v>
       </c>
       <c r="N42">
-        <v>45.6267791111111</v>
+        <v>45.3496708111111</v>
       </c>
       <c r="O42">
-        <v>10.2660253</v>
+        <v>10.2036759325</v>
       </c>
       <c r="P42">
-        <v>35.3607538111111</v>
+        <v>35.1459948786111</v>
       </c>
       <c r="Q42">
-        <v>56.7607538111111</v>
+        <v>56.5459948786111</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2490686158470405</v>
+        <v>0.2520027409593791</v>
       </c>
       <c r="T42">
-        <v>1.417278747196577</v>
+        <v>1.437736765991089</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>5.116330971601274</v>
+        <v>4.991542411318315</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1662531921660337</v>
+        <v>0.165922214823843</v>
       </c>
       <c r="C43">
-        <v>376.5476813931919</v>
+        <v>372.9405226365827</v>
       </c>
       <c r="D43">
-        <v>509.4986813931919</v>
+        <v>510.9025226365828</v>
       </c>
       <c r="E43">
-        <v>31.45100000000002</v>
+        <v>36.46200000000002</v>
       </c>
       <c r="F43">
-        <v>205.451</v>
+        <v>210.462</v>
       </c>
       <c r="G43">
         <v>72.5</v>
@@ -4813,28 +4813,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M43">
-        <v>11.3614403</v>
+        <v>11.6385486</v>
       </c>
       <c r="N43">
-        <v>45.3496708111111</v>
+        <v>45.0725625111111</v>
       </c>
       <c r="O43">
-        <v>10.2036759325</v>
+        <v>10.141326565</v>
       </c>
       <c r="P43">
-        <v>35.1459948786111</v>
+        <v>34.9312359461111</v>
       </c>
       <c r="Q43">
-        <v>56.5459948786111</v>
+        <v>56.3312359461111</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2520027409593791</v>
+        <v>0.2550380427997293</v>
       </c>
       <c r="T43">
-        <v>1.437736765991089</v>
+        <v>1.45890023370955</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.991542411318315</v>
+        <v>4.872696163429785</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.165922214823843</v>
+        <v>0.1655912374816524</v>
       </c>
       <c r="C44">
-        <v>372.9405226365827</v>
+        <v>369.3411213696423</v>
       </c>
       <c r="D44">
-        <v>510.9025226365827</v>
+        <v>512.3141213696423</v>
       </c>
       <c r="E44">
-        <v>36.46199999999999</v>
+        <v>41.47300000000001</v>
       </c>
       <c r="F44">
-        <v>210.462</v>
+        <v>215.473</v>
       </c>
       <c r="G44">
         <v>72.5</v>
@@ -4895,28 +4895,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M44">
-        <v>11.6385486</v>
+        <v>11.9156569</v>
       </c>
       <c r="N44">
-        <v>45.0725625111111</v>
+        <v>44.7954542111111</v>
       </c>
       <c r="O44">
-        <v>10.141326565</v>
+        <v>10.0789771975</v>
       </c>
       <c r="P44">
-        <v>34.9312359461111</v>
+        <v>34.7164770136111</v>
       </c>
       <c r="Q44">
-        <v>56.3312359461111</v>
+        <v>56.1164770136111</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2550380427997293</v>
+        <v>0.2581798464590392</v>
       </c>
       <c r="T44">
-        <v>1.45890023370955</v>
+        <v>1.480806279242693</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.872696163429786</v>
+        <v>4.759377648001185</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1655912374816524</v>
+        <v>0.1652602601394617</v>
       </c>
       <c r="C45">
-        <v>369.3411213696423</v>
+        <v>365.7495420712189</v>
       </c>
       <c r="D45">
-        <v>512.3141213696423</v>
+        <v>513.7335420712189</v>
       </c>
       <c r="E45">
-        <v>41.47300000000001</v>
+        <v>46.48400000000001</v>
       </c>
       <c r="F45">
-        <v>215.473</v>
+        <v>220.484</v>
       </c>
       <c r="G45">
         <v>72.5</v>
@@ -4977,28 +4977,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M45">
-        <v>11.9156569</v>
+        <v>12.1927652</v>
       </c>
       <c r="N45">
-        <v>44.7954542111111</v>
+        <v>44.5183459111111</v>
       </c>
       <c r="O45">
-        <v>10.0789771975</v>
+        <v>10.01662783</v>
       </c>
       <c r="P45">
-        <v>34.7164770136111</v>
+        <v>34.5017180811111</v>
       </c>
       <c r="Q45">
-        <v>56.1164770136111</v>
+        <v>55.9017180811111</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2581798464590392</v>
+        <v>0.2614338573918958</v>
       </c>
       <c r="T45">
-        <v>1.480806279242693</v>
+        <v>1.503494683544877</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.759377648001185</v>
+        <v>4.651209974182977</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1652602601394617</v>
+        <v>0.164929282797271</v>
       </c>
       <c r="C46">
-        <v>365.7495420712189</v>
+        <v>362.1658499367275</v>
       </c>
       <c r="D46">
-        <v>513.7335420712189</v>
+        <v>515.1608499367275</v>
       </c>
       <c r="E46">
-        <v>46.48400000000001</v>
+        <v>51.495</v>
       </c>
       <c r="F46">
-        <v>220.484</v>
+        <v>225.495</v>
       </c>
       <c r="G46">
         <v>72.5</v>
@@ -5059,28 +5059,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M46">
-        <v>12.1927652</v>
+        <v>12.4698735</v>
       </c>
       <c r="N46">
-        <v>44.5183459111111</v>
+        <v>44.2412376111111</v>
       </c>
       <c r="O46">
-        <v>10.01662783</v>
+        <v>9.954278462499998</v>
       </c>
       <c r="P46">
-        <v>34.5017180811111</v>
+        <v>34.2869591486111</v>
       </c>
       <c r="Q46">
-        <v>55.9017180811111</v>
+        <v>55.6869591486111</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2614338573918958</v>
+        <v>0.2648061959950382</v>
       </c>
       <c r="T46">
-        <v>1.503494683544877</v>
+        <v>1.527008120730778</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>4.651209974182977</v>
+        <v>4.547849752534466</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.164929282797271</v>
+        <v>0.1654895554550803</v>
       </c>
       <c r="C47">
-        <v>362.1658499367275</v>
+        <v>354.7433568244342</v>
       </c>
       <c r="D47">
-        <v>515.1608499367275</v>
+        <v>512.7493568244342</v>
       </c>
       <c r="E47">
-        <v>51.495</v>
+        <v>56.50600000000003</v>
       </c>
       <c r="F47">
-        <v>225.495</v>
+        <v>230.506</v>
       </c>
       <c r="G47">
         <v>72.5</v>
@@ -5141,45 +5141,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M47">
-        <v>12.4698735</v>
+        <v>13.3232468</v>
       </c>
       <c r="N47">
-        <v>44.2412376111111</v>
+        <v>43.3878643111111</v>
       </c>
       <c r="O47">
-        <v>9.954278462499998</v>
+        <v>9.762269469999998</v>
       </c>
       <c r="P47">
-        <v>34.2869591486111</v>
+        <v>33.6255948411111</v>
       </c>
       <c r="Q47">
-        <v>55.6869591486111</v>
+        <v>55.0255948411111</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2648061959950382</v>
+        <v>0.2683034360279265</v>
       </c>
       <c r="T47">
-        <v>1.527008120730778</v>
+        <v>1.5513924259606</v>
       </c>
       <c r="U47">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V47">
         <v>0.225</v>
       </c>
       <c r="W47">
-        <v>0.0428575</v>
+        <v>0.044795</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y47">
-        <v>4.547849752534466</v>
+        <v>4.256553373394771</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1654895554550803</v>
+        <v>0.1651779531128897</v>
       </c>
       <c r="C48">
-        <v>354.7433568244342</v>
+        <v>351.0707438245208</v>
       </c>
       <c r="D48">
-        <v>512.7493568244342</v>
+        <v>514.0877438245209</v>
       </c>
       <c r="E48">
-        <v>56.50600000000003</v>
+        <v>61.51700000000002</v>
       </c>
       <c r="F48">
-        <v>230.506</v>
+        <v>235.517</v>
       </c>
       <c r="G48">
         <v>72.5</v>
@@ -5223,28 +5223,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M48">
-        <v>13.3232468</v>
+        <v>13.6128826</v>
       </c>
       <c r="N48">
-        <v>43.3878643111111</v>
+        <v>43.0982285111111</v>
       </c>
       <c r="O48">
-        <v>9.762269469999998</v>
+        <v>9.697101414999999</v>
       </c>
       <c r="P48">
-        <v>33.6255948411111</v>
+        <v>33.4011270961111</v>
       </c>
       <c r="Q48">
-        <v>55.0255948411111</v>
+        <v>54.8011270961111</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2683034360279265</v>
+        <v>0.2719326473828107</v>
       </c>
       <c r="T48">
-        <v>1.5513924259606</v>
+        <v>1.576696893651925</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.256553373394771</v>
+        <v>4.165988408003393</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1651779531128897</v>
+        <v>0.1648663507706991</v>
       </c>
       <c r="C49">
-        <v>351.0707438245208</v>
+        <v>347.4051360703596</v>
       </c>
       <c r="D49">
-        <v>514.0877438245209</v>
+        <v>515.4331360703596</v>
       </c>
       <c r="E49">
-        <v>61.51700000000002</v>
+        <v>66.52800000000002</v>
       </c>
       <c r="F49">
-        <v>235.517</v>
+        <v>240.528</v>
       </c>
       <c r="G49">
         <v>72.5</v>
@@ -5305,28 +5305,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M49">
-        <v>13.6128826</v>
+        <v>13.9025184</v>
       </c>
       <c r="N49">
-        <v>43.0982285111111</v>
+        <v>42.8085927111111</v>
       </c>
       <c r="O49">
-        <v>9.697101414999999</v>
+        <v>9.631933359999998</v>
       </c>
       <c r="P49">
-        <v>33.4011270961111</v>
+        <v>33.17665935111111</v>
       </c>
       <c r="Q49">
-        <v>54.8011270961111</v>
+        <v>54.5766593511111</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2719326473828107</v>
+        <v>0.2757014437898058</v>
       </c>
       <c r="T49">
-        <v>1.576696893651925</v>
+        <v>1.602974610100609</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>4.165988408003393</v>
+        <v>4.079196982836656</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1648663507706991</v>
+        <v>0.1658838734285083</v>
       </c>
       <c r="C50">
-        <v>347.4051360703596</v>
+        <v>338.0266479175934</v>
       </c>
       <c r="D50">
-        <v>515.4331360703596</v>
+        <v>511.0656479175935</v>
       </c>
       <c r="E50">
-        <v>66.52799999999999</v>
+        <v>71.53900000000002</v>
       </c>
       <c r="F50">
-        <v>240.528</v>
+        <v>245.539</v>
       </c>
       <c r="G50">
         <v>72.5</v>
@@ -5387,45 +5387,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M50">
-        <v>13.9025184</v>
+        <v>15.0515407</v>
       </c>
       <c r="N50">
-        <v>42.8085927111111</v>
+        <v>41.6595704111111</v>
       </c>
       <c r="O50">
-        <v>9.631933359999998</v>
+        <v>9.3734033425</v>
       </c>
       <c r="P50">
-        <v>33.17665935111111</v>
+        <v>32.28616706861111</v>
       </c>
       <c r="Q50">
-        <v>54.5766593511111</v>
+        <v>53.68616706861111</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2757014437898058</v>
+        <v>0.2796180361343301</v>
       </c>
       <c r="T50">
-        <v>1.602974610100609</v>
+        <v>1.630282825233554</v>
       </c>
       <c r="U50">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V50">
         <v>0.225</v>
       </c>
       <c r="W50">
-        <v>0.044795</v>
+        <v>0.0475075</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y50">
-        <v>4.079196982836656</v>
+        <v>3.767794423271972</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1658838734285083</v>
+        <v>0.1655993960863177</v>
       </c>
       <c r="C51">
-        <v>338.0266479175934</v>
+        <v>334.2292316413361</v>
       </c>
       <c r="D51">
-        <v>511.0656479175935</v>
+        <v>512.2792316413361</v>
       </c>
       <c r="E51">
-        <v>71.53900000000002</v>
+        <v>76.55000000000001</v>
       </c>
       <c r="F51">
-        <v>245.539</v>
+        <v>250.55</v>
       </c>
       <c r="G51">
         <v>72.5</v>
@@ -5469,28 +5469,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M51">
-        <v>15.0515407</v>
+        <v>15.358715</v>
       </c>
       <c r="N51">
-        <v>41.6595704111111</v>
+        <v>41.3523961111111</v>
       </c>
       <c r="O51">
-        <v>9.3734033425</v>
+        <v>9.304289124999999</v>
       </c>
       <c r="P51">
-        <v>32.28616706861111</v>
+        <v>32.04810698611111</v>
       </c>
       <c r="Q51">
-        <v>53.68616706861111</v>
+        <v>53.44810698611111</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2796180361343301</v>
+        <v>0.2836912921726353</v>
       </c>
       <c r="T51">
-        <v>1.630282825233554</v>
+        <v>1.658683368971818</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.767794423271972</v>
+        <v>3.692438534806532</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1655993960863177</v>
+        <v>0.165314918744127</v>
       </c>
       <c r="C52">
-        <v>334.2292316413361</v>
+        <v>330.437592670136</v>
       </c>
       <c r="D52">
-        <v>512.2792316413361</v>
+        <v>513.4985926701361</v>
       </c>
       <c r="E52">
-        <v>76.55000000000001</v>
+        <v>81.56100000000001</v>
       </c>
       <c r="F52">
-        <v>250.55</v>
+        <v>255.561</v>
       </c>
       <c r="G52">
         <v>72.5</v>
@@ -5551,28 +5551,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M52">
-        <v>15.358715</v>
+        <v>15.6658893</v>
       </c>
       <c r="N52">
-        <v>41.3523961111111</v>
+        <v>41.04522181111111</v>
       </c>
       <c r="O52">
-        <v>9.304289124999999</v>
+        <v>9.235174907499999</v>
       </c>
       <c r="P52">
-        <v>32.04810698611111</v>
+        <v>31.81004690361111</v>
       </c>
       <c r="Q52">
-        <v>53.44810698611111</v>
+        <v>53.2100469036111</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2836912921726353</v>
+        <v>0.2879308035594429</v>
       </c>
       <c r="T52">
-        <v>1.658683368971818</v>
+        <v>1.68824311857695</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.692438534806532</v>
+        <v>3.62003777922209</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.165314918744127</v>
+        <v>0.1650304414019363</v>
       </c>
       <c r="C53">
-        <v>330.437592670136</v>
+        <v>326.6517723569998</v>
       </c>
       <c r="D53">
-        <v>513.4985926701361</v>
+        <v>514.7237723569998</v>
       </c>
       <c r="E53">
-        <v>81.56100000000001</v>
+        <v>86.572</v>
       </c>
       <c r="F53">
-        <v>255.561</v>
+        <v>260.572</v>
       </c>
       <c r="G53">
         <v>72.5</v>
@@ -5633,28 +5633,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M53">
-        <v>15.6658893</v>
+        <v>15.9730636</v>
       </c>
       <c r="N53">
-        <v>41.04522181111111</v>
+        <v>40.73804751111111</v>
       </c>
       <c r="O53">
-        <v>9.235174907499999</v>
+        <v>9.166060689999998</v>
       </c>
       <c r="P53">
-        <v>31.81004690361111</v>
+        <v>31.57198682111111</v>
       </c>
       <c r="Q53">
-        <v>53.2100469036111</v>
+        <v>52.9719868211111</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2879308035594429</v>
+        <v>0.2923469612540341</v>
       </c>
       <c r="T53">
-        <v>1.68824311857695</v>
+        <v>1.719034524415629</v>
       </c>
       <c r="U53">
         <v>0.0613</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.62003777922209</v>
+        <v>3.550421668083204</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1650304414019363</v>
+        <v>0.1658960640597457</v>
       </c>
       <c r="C54">
-        <v>326.6517723569998</v>
+        <v>317.9307710063838</v>
       </c>
       <c r="D54">
-        <v>514.7237723569998</v>
+        <v>511.0137710063839</v>
       </c>
       <c r="E54">
-        <v>86.572</v>
+        <v>91.58300000000003</v>
       </c>
       <c r="F54">
-        <v>260.572</v>
+        <v>265.583</v>
       </c>
       <c r="G54">
         <v>72.5</v>
@@ -5715,45 +5715,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M54">
-        <v>15.9730636</v>
+        <v>17.0238703</v>
       </c>
       <c r="N54">
-        <v>40.73804751111111</v>
+        <v>39.6872408111111</v>
       </c>
       <c r="O54">
-        <v>9.166060689999998</v>
+        <v>8.929629182499998</v>
       </c>
       <c r="P54">
-        <v>31.57198682111111</v>
+        <v>30.7576116286111</v>
       </c>
       <c r="Q54">
-        <v>52.9719868211111</v>
+        <v>52.15761162861109</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2923469612540341</v>
+        <v>0.2969510405526504</v>
       </c>
       <c r="T54">
-        <v>1.719034524415629</v>
+        <v>1.751136202843187</v>
       </c>
       <c r="U54">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V54">
         <v>0.225</v>
       </c>
       <c r="W54">
-        <v>0.0475075</v>
+        <v>0.04967750000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y54">
-        <v>3.550421668083204</v>
+        <v>3.331270158414628</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1658960640597457</v>
+        <v>0.165633286717555</v>
       </c>
       <c r="C55">
-        <v>317.9307710063838</v>
+        <v>314.0403514748507</v>
       </c>
       <c r="D55">
-        <v>511.0137710063839</v>
+        <v>512.1343514748507</v>
       </c>
       <c r="E55">
-        <v>91.58300000000003</v>
+        <v>96.59400000000005</v>
       </c>
       <c r="F55">
-        <v>265.583</v>
+        <v>270.5940000000001</v>
       </c>
       <c r="G55">
         <v>72.5</v>
@@ -5797,28 +5797,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M55">
-        <v>17.0238703</v>
+        <v>17.34507540000001</v>
       </c>
       <c r="N55">
-        <v>39.6872408111111</v>
+        <v>39.3660357111111</v>
       </c>
       <c r="O55">
-        <v>8.929629182499998</v>
+        <v>8.857358034999997</v>
       </c>
       <c r="P55">
-        <v>30.7576116286111</v>
+        <v>30.5086776761111</v>
       </c>
       <c r="Q55">
-        <v>52.15761162861109</v>
+        <v>51.9086776761111</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2969510405526504</v>
+        <v>0.3017552972120762</v>
       </c>
       <c r="T55">
-        <v>1.751136202843187</v>
+        <v>1.78463360641977</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.331270158414628</v>
+        <v>3.269579970295839</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.165633286717555</v>
+        <v>0.1653705093753644</v>
       </c>
       <c r="C56">
-        <v>314.0403514748507</v>
+        <v>310.1548572908595</v>
       </c>
       <c r="D56">
-        <v>512.1343514748507</v>
+        <v>513.2598572908595</v>
       </c>
       <c r="E56">
-        <v>96.59400000000005</v>
+        <v>101.605</v>
       </c>
       <c r="F56">
-        <v>270.5940000000001</v>
+        <v>275.605</v>
       </c>
       <c r="G56">
         <v>72.5</v>
@@ -5879,28 +5879,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M56">
-        <v>17.34507540000001</v>
+        <v>17.6662805</v>
       </c>
       <c r="N56">
-        <v>39.3660357111111</v>
+        <v>39.0448306111111</v>
       </c>
       <c r="O56">
-        <v>8.857358034999997</v>
+        <v>8.785086887499997</v>
       </c>
       <c r="P56">
-        <v>30.5086776761111</v>
+        <v>30.2597437236111</v>
       </c>
       <c r="Q56">
-        <v>51.9086776761111</v>
+        <v>51.6597437236111</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3017552972120762</v>
+        <v>0.3067730763896986</v>
       </c>
       <c r="T56">
-        <v>1.78463360641977</v>
+        <v>1.819619783488646</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.269579970295839</v>
+        <v>3.210133061745005</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1653705093753644</v>
+        <v>0.1651077320331737</v>
       </c>
       <c r="C57">
-        <v>310.1548572908595</v>
+        <v>306.2743209988994</v>
       </c>
       <c r="D57">
-        <v>513.2598572908595</v>
+        <v>514.3903209988995</v>
       </c>
       <c r="E57">
-        <v>101.605</v>
+        <v>106.616</v>
       </c>
       <c r="F57">
-        <v>275.605</v>
+        <v>280.616</v>
       </c>
       <c r="G57">
         <v>72.5</v>
@@ -5961,28 +5961,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M57">
-        <v>17.6662805</v>
+        <v>17.9874856</v>
       </c>
       <c r="N57">
-        <v>39.0448306111111</v>
+        <v>38.72362551111109</v>
       </c>
       <c r="O57">
-        <v>8.785086887499997</v>
+        <v>8.712815739999996</v>
       </c>
       <c r="P57">
-        <v>30.2597437236111</v>
+        <v>30.0108097711111</v>
       </c>
       <c r="Q57">
-        <v>51.6597437236111</v>
+        <v>51.4108097711111</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3067730763896986</v>
+        <v>0.3120189364390311</v>
       </c>
       <c r="T57">
-        <v>1.819619783488646</v>
+        <v>1.856196241333379</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.210133061745005</v>
+        <v>3.152809257070988</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1651077320331737</v>
+        <v>0.164844954690983</v>
       </c>
       <c r="C58">
-        <v>306.2743209988994</v>
+        <v>302.3987754308118</v>
       </c>
       <c r="D58">
-        <v>514.3903209988995</v>
+        <v>515.5257754308119</v>
       </c>
       <c r="E58">
-        <v>106.616</v>
+        <v>111.6270000000001</v>
       </c>
       <c r="F58">
-        <v>280.616</v>
+        <v>285.6270000000001</v>
       </c>
       <c r="G58">
         <v>72.5</v>
@@ -6043,28 +6043,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M58">
-        <v>17.9874856</v>
+        <v>18.30869070000001</v>
       </c>
       <c r="N58">
-        <v>38.72362551111109</v>
+        <v>38.40242041111109</v>
       </c>
       <c r="O58">
-        <v>8.712815739999996</v>
+        <v>8.640544592499996</v>
       </c>
       <c r="P58">
-        <v>30.0108097711111</v>
+        <v>29.7618758186111</v>
       </c>
       <c r="Q58">
-        <v>51.4108097711111</v>
+        <v>51.16187581861109</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.3120189364390311</v>
+        <v>0.3175087899790303</v>
       </c>
       <c r="T58">
-        <v>1.856196241333379</v>
+        <v>1.894473929775542</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.152809257070988</v>
+        <v>3.097496813964479</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.164844954690983</v>
+        <v>0.1645821773487924</v>
       </c>
       <c r="C59">
-        <v>302.3987754308118</v>
+        <v>298.5282537089689</v>
       </c>
       <c r="D59">
-        <v>515.5257754308119</v>
+        <v>516.666253708969</v>
       </c>
       <c r="E59">
-        <v>111.6270000000001</v>
+        <v>116.638</v>
       </c>
       <c r="F59">
-        <v>285.6270000000001</v>
+        <v>290.638</v>
       </c>
       <c r="G59">
         <v>72.5</v>
@@ -6125,28 +6125,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M59">
-        <v>18.30869070000001</v>
+        <v>18.6298958</v>
       </c>
       <c r="N59">
-        <v>38.40242041111109</v>
+        <v>38.08121531111109</v>
       </c>
       <c r="O59">
-        <v>8.640544592499996</v>
+        <v>8.568273444999997</v>
       </c>
       <c r="P59">
-        <v>29.7618758186111</v>
+        <v>29.5129418661111</v>
       </c>
       <c r="Q59">
-        <v>51.16187581861109</v>
+        <v>50.9129418661111</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3175087899790303</v>
+        <v>0.3232600651161723</v>
       </c>
       <c r="T59">
-        <v>1.894473929775542</v>
+        <v>1.93457436528638</v>
       </c>
       <c r="U59">
         <v>0.0641</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>3.097496813964479</v>
+        <v>3.044091696482333</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1645821773487924</v>
+        <v>0.1678859500066017</v>
       </c>
       <c r="C60">
-        <v>298.528253708969</v>
+        <v>279.5357280532797</v>
       </c>
       <c r="D60">
-        <v>516.666253708969</v>
+        <v>502.6847280532797</v>
       </c>
       <c r="E60">
-        <v>116.638</v>
+        <v>121.649</v>
       </c>
       <c r="F60">
-        <v>290.638</v>
+        <v>295.649</v>
       </c>
       <c r="G60">
         <v>72.5</v>
@@ -6207,45 +6207,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M60">
-        <v>18.6298958</v>
+        <v>21.2571631</v>
       </c>
       <c r="N60">
-        <v>38.0812153111111</v>
+        <v>35.45394801111109</v>
       </c>
       <c r="O60">
-        <v>8.568273444999997</v>
+        <v>7.977138302499997</v>
       </c>
       <c r="P60">
-        <v>29.51294186611111</v>
+        <v>27.4768097086111</v>
       </c>
       <c r="Q60">
-        <v>50.9129418661111</v>
+        <v>48.8768097086111</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3232600651161722</v>
+        <v>0.3292918902600042</v>
       </c>
       <c r="T60">
-        <v>1.934574365286379</v>
+        <v>1.976630919602623</v>
       </c>
       <c r="U60">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V60">
         <v>0.225</v>
       </c>
       <c r="W60">
-        <v>0.04967750000000001</v>
+        <v>0.05572250000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y60">
-        <v>3.044091696482333</v>
+        <v>2.667858869235053</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1678859500066017</v>
+        <v>0.167683622664411</v>
       </c>
       <c r="C61">
-        <v>279.5357280532797</v>
+        <v>275.3591868818208</v>
       </c>
       <c r="D61">
-        <v>502.6847280532797</v>
+        <v>503.5191868818208</v>
       </c>
       <c r="E61">
-        <v>121.649</v>
+        <v>126.66</v>
       </c>
       <c r="F61">
-        <v>295.649</v>
+        <v>300.66</v>
       </c>
       <c r="G61">
         <v>72.5</v>
@@ -6289,28 +6289,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M61">
-        <v>21.2571631</v>
+        <v>21.617454</v>
       </c>
       <c r="N61">
-        <v>35.45394801111109</v>
+        <v>35.0936571111111</v>
       </c>
       <c r="O61">
-        <v>7.977138302499997</v>
+        <v>7.896072849999998</v>
       </c>
       <c r="P61">
-        <v>27.4768097086111</v>
+        <v>27.1975842611111</v>
       </c>
       <c r="Q61">
-        <v>48.8768097086111</v>
+        <v>48.5975842611111</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3292918902600042</v>
+        <v>0.3356253066610275</v>
       </c>
       <c r="T61">
-        <v>1.976630919602623</v>
+        <v>2.020790301634679</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.667858869235053</v>
+        <v>2.623394554747802</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.167683622664411</v>
+        <v>0.1674812953222204</v>
       </c>
       <c r="C62">
-        <v>275.3591868818208</v>
+        <v>271.1854207274502</v>
       </c>
       <c r="D62">
-        <v>503.5191868818208</v>
+        <v>504.3564207274502</v>
       </c>
       <c r="E62">
-        <v>126.66</v>
+        <v>131.671</v>
       </c>
       <c r="F62">
-        <v>300.66</v>
+        <v>305.671</v>
       </c>
       <c r="G62">
         <v>72.5</v>
@@ -6371,28 +6371,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M62">
-        <v>21.617454</v>
+        <v>21.9777449</v>
       </c>
       <c r="N62">
-        <v>35.0936571111111</v>
+        <v>34.7333662111111</v>
       </c>
       <c r="O62">
-        <v>7.896072849999998</v>
+        <v>7.815007397499999</v>
       </c>
       <c r="P62">
-        <v>27.1975842611111</v>
+        <v>26.91835881361111</v>
       </c>
       <c r="Q62">
-        <v>48.5975842611111</v>
+        <v>48.31835881361111</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.3356253066610275</v>
+        <v>0.3422835136467189</v>
       </c>
       <c r="T62">
-        <v>2.020790301634679</v>
+        <v>2.067214267360688</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.623394554747802</v>
+        <v>2.580388086637183</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1674812953222204</v>
+        <v>0.1672789679800297</v>
       </c>
       <c r="C63">
-        <v>271.1854207274502</v>
+        <v>267.0144434558237</v>
       </c>
       <c r="D63">
-        <v>504.3564207274502</v>
+        <v>505.1964434558237</v>
       </c>
       <c r="E63">
-        <v>131.671</v>
+        <v>136.682</v>
       </c>
       <c r="F63">
-        <v>305.671</v>
+        <v>310.682</v>
       </c>
       <c r="G63">
         <v>72.5</v>
@@ -6453,28 +6453,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M63">
-        <v>21.9777449</v>
+        <v>22.3380358</v>
       </c>
       <c r="N63">
-        <v>34.7333662111111</v>
+        <v>34.37307531111109</v>
       </c>
       <c r="O63">
-        <v>7.815007397499999</v>
+        <v>7.733941944999996</v>
       </c>
       <c r="P63">
-        <v>26.91835881361111</v>
+        <v>26.6391333661111</v>
       </c>
       <c r="Q63">
-        <v>48.31835881361111</v>
+        <v>48.03913336611109</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3422835136467189</v>
+        <v>0.3492921525790255</v>
       </c>
       <c r="T63">
-        <v>2.067214267360688</v>
+        <v>2.116081599703854</v>
       </c>
       <c r="U63">
         <v>0.07190000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.580388086637183</v>
+        <v>2.538768923949486</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1672789679800297</v>
+        <v>0.168980815637839</v>
       </c>
       <c r="C64">
-        <v>267.0144434558237</v>
+        <v>255.0237252295969</v>
       </c>
       <c r="D64">
-        <v>505.1964434558237</v>
+        <v>498.216725229597</v>
       </c>
       <c r="E64">
-        <v>136.682</v>
+        <v>141.693</v>
       </c>
       <c r="F64">
-        <v>310.682</v>
+        <v>315.693</v>
       </c>
       <c r="G64">
         <v>72.5</v>
@@ -6535,45 +6535,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M64">
-        <v>22.3380358</v>
+        <v>23.9295294</v>
       </c>
       <c r="N64">
-        <v>34.37307531111109</v>
+        <v>32.7815817111111</v>
       </c>
       <c r="O64">
-        <v>7.733941944999996</v>
+        <v>7.375855884999998</v>
       </c>
       <c r="P64">
-        <v>26.6391333661111</v>
+        <v>25.4057258261111</v>
       </c>
       <c r="Q64">
-        <v>48.03913336611109</v>
+        <v>46.8057258261111</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3492921525790255</v>
+        <v>0.3566796368590244</v>
       </c>
       <c r="T64">
-        <v>2.116081599703854</v>
+        <v>2.167590409470975</v>
       </c>
       <c r="U64">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V64">
         <v>0.225</v>
       </c>
       <c r="W64">
-        <v>0.05572250000000001</v>
+        <v>0.05874500000000001</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.538768923949486</v>
+        <v>2.369921704816774</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.168980815637839</v>
+        <v>0.1688087132956484</v>
       </c>
       <c r="C65">
-        <v>255.0237252295969</v>
+        <v>250.7097836983289</v>
       </c>
       <c r="D65">
-        <v>498.216725229597</v>
+        <v>498.9137836983289</v>
       </c>
       <c r="E65">
-        <v>141.693</v>
+        <v>146.704</v>
       </c>
       <c r="F65">
-        <v>315.693</v>
+        <v>320.704</v>
       </c>
       <c r="G65">
         <v>72.5</v>
@@ -6617,28 +6617,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M65">
-        <v>23.9295294</v>
+        <v>24.3093632</v>
       </c>
       <c r="N65">
-        <v>32.7815817111111</v>
+        <v>32.4017479111111</v>
       </c>
       <c r="O65">
-        <v>7.375855884999998</v>
+        <v>7.290393279999998</v>
       </c>
       <c r="P65">
-        <v>25.4057258261111</v>
+        <v>25.11135463111111</v>
       </c>
       <c r="Q65">
-        <v>46.8057258261111</v>
+        <v>46.5113546311111</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3566796368590244</v>
+        <v>0.3644775369323567</v>
       </c>
       <c r="T65">
-        <v>2.167590409470975</v>
+        <v>2.221960819780715</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.369921704816774</v>
+        <v>2.332891678179011</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1688087132956484</v>
+        <v>0.1686366109534577</v>
       </c>
       <c r="C66">
-        <v>250.7097836983289</v>
+        <v>246.3977954185256</v>
       </c>
       <c r="D66">
-        <v>498.9137836983289</v>
+        <v>499.6127954185256</v>
       </c>
       <c r="E66">
-        <v>146.704</v>
+        <v>151.715</v>
       </c>
       <c r="F66">
-        <v>320.704</v>
+        <v>325.715</v>
       </c>
       <c r="G66">
         <v>72.5</v>
@@ -6699,28 +6699,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M66">
-        <v>24.3093632</v>
+        <v>24.689197</v>
       </c>
       <c r="N66">
-        <v>32.4017479111111</v>
+        <v>32.0219141111111</v>
       </c>
       <c r="O66">
-        <v>7.290393279999998</v>
+        <v>7.204930674999998</v>
       </c>
       <c r="P66">
-        <v>25.11135463111111</v>
+        <v>24.8169834361111</v>
       </c>
       <c r="Q66">
-        <v>46.5113546311111</v>
+        <v>46.2169834361111</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3644775369323567</v>
+        <v>0.3727210312955935</v>
       </c>
       <c r="T66">
-        <v>2.221960819780715</v>
+        <v>2.279438110679581</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.332891678179011</v>
+        <v>2.297001036976257</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1686366109534577</v>
+        <v>0.168464508611267</v>
       </c>
       <c r="C67">
-        <v>246.3977954185256</v>
+        <v>242.0877686116148</v>
       </c>
       <c r="D67">
-        <v>499.6127954185256</v>
+        <v>500.3137686116148</v>
       </c>
       <c r="E67">
-        <v>151.715</v>
+        <v>156.7260000000001</v>
       </c>
       <c r="F67">
-        <v>325.715</v>
+        <v>330.7260000000001</v>
       </c>
       <c r="G67">
         <v>72.5</v>
@@ -6781,28 +6781,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M67">
-        <v>24.689197</v>
+        <v>25.06903080000001</v>
       </c>
       <c r="N67">
-        <v>32.0219141111111</v>
+        <v>31.64208031111109</v>
       </c>
       <c r="O67">
-        <v>7.204930674999998</v>
+        <v>7.119468069999996</v>
       </c>
       <c r="P67">
-        <v>24.8169834361111</v>
+        <v>24.5226122411111</v>
       </c>
       <c r="Q67">
-        <v>46.2169834361111</v>
+        <v>45.9226122411111</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3727210312955935</v>
+        <v>0.3814494370919619</v>
       </c>
       <c r="T67">
-        <v>2.279438110679581</v>
+        <v>2.340296418690146</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.297001036976257</v>
+        <v>2.262197990961465</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.168464508611267</v>
+        <v>0.1682924062690764</v>
       </c>
       <c r="C68">
-        <v>242.0877686116148</v>
+        <v>237.7797115452294</v>
       </c>
       <c r="D68">
-        <v>500.3137686116148</v>
+        <v>501.0167115452294</v>
       </c>
       <c r="E68">
-        <v>156.7260000000001</v>
+        <v>161.737</v>
       </c>
       <c r="F68">
-        <v>330.7260000000001</v>
+        <v>335.737</v>
       </c>
       <c r="G68">
         <v>72.5</v>
@@ -6863,28 +6863,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M68">
-        <v>25.06903080000001</v>
+        <v>25.4488646</v>
       </c>
       <c r="N68">
-        <v>31.64208031111109</v>
+        <v>31.2622465111111</v>
       </c>
       <c r="O68">
-        <v>7.119468069999996</v>
+        <v>7.034005464999997</v>
       </c>
       <c r="P68">
-        <v>24.5226122411111</v>
+        <v>24.2282410461111</v>
       </c>
       <c r="Q68">
-        <v>45.9226122411111</v>
+        <v>45.6282410461111</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3814494370919619</v>
+        <v>0.3907068371790194</v>
       </c>
       <c r="T68">
-        <v>2.340296418690146</v>
+        <v>2.404843109004382</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.262197990961465</v>
+        <v>2.228433841842637</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1682924062690764</v>
+        <v>0.1681203039268857</v>
       </c>
       <c r="C69">
-        <v>237.7797115452294</v>
+        <v>233.4736325335318</v>
       </c>
       <c r="D69">
-        <v>501.0167115452294</v>
+        <v>501.7216325335319</v>
       </c>
       <c r="E69">
-        <v>161.737</v>
+        <v>166.748</v>
       </c>
       <c r="F69">
-        <v>335.737</v>
+        <v>340.748</v>
       </c>
       <c r="G69">
         <v>72.5</v>
@@ -6945,28 +6945,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M69">
-        <v>25.4488646</v>
+        <v>25.8286984</v>
       </c>
       <c r="N69">
-        <v>31.2622465111111</v>
+        <v>30.8824127111111</v>
       </c>
       <c r="O69">
-        <v>7.034005464999997</v>
+        <v>6.948542859999997</v>
       </c>
       <c r="P69">
-        <v>24.2282410461111</v>
+        <v>23.9338698511111</v>
       </c>
       <c r="Q69">
-        <v>45.6282410461111</v>
+        <v>45.3338698511111</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3907068371790194</v>
+        <v>0.4005428247715179</v>
       </c>
       <c r="T69">
-        <v>2.404843109004382</v>
+        <v>2.473423967463257</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.228433841842637</v>
+        <v>2.195662755933187</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1681203039268857</v>
+        <v>0.1679482015846951</v>
       </c>
       <c r="C70">
-        <v>233.4736325335318</v>
+        <v>229.1695399375419</v>
       </c>
       <c r="D70">
-        <v>501.7216325335319</v>
+        <v>502.4285399375419</v>
       </c>
       <c r="E70">
-        <v>166.748</v>
+        <v>171.7590000000001</v>
       </c>
       <c r="F70">
-        <v>340.748</v>
+        <v>345.7590000000001</v>
       </c>
       <c r="G70">
         <v>72.5</v>
@@ -7027,28 +7027,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M70">
-        <v>25.8286984</v>
+        <v>26.20853220000001</v>
       </c>
       <c r="N70">
-        <v>30.8824127111111</v>
+        <v>30.50257891111109</v>
       </c>
       <c r="O70">
-        <v>6.948542859999997</v>
+        <v>6.863080254999996</v>
       </c>
       <c r="P70">
-        <v>23.9338698511111</v>
+        <v>23.6394986561111</v>
       </c>
       <c r="Q70">
-        <v>45.3338698511111</v>
+        <v>45.03949865611109</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.4005428247715179</v>
+        <v>0.4110133922086938</v>
       </c>
       <c r="T70">
-        <v>2.473423967463257</v>
+        <v>2.546429397435609</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.195662755933187</v>
+        <v>2.163841556571836</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1679482015846951</v>
+        <v>0.1677760992425044</v>
       </c>
       <c r="C71">
-        <v>229.1695399375419</v>
+        <v>224.8674421654677</v>
       </c>
       <c r="D71">
-        <v>502.4285399375419</v>
+        <v>503.1374421654677</v>
       </c>
       <c r="E71">
-        <v>171.7590000000001</v>
+        <v>176.77</v>
       </c>
       <c r="F71">
-        <v>345.7590000000001</v>
+        <v>350.77</v>
       </c>
       <c r="G71">
         <v>72.5</v>
@@ -7109,28 +7109,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M71">
-        <v>26.20853220000001</v>
+        <v>26.588366</v>
       </c>
       <c r="N71">
-        <v>30.50257891111109</v>
+        <v>30.1227451111111</v>
       </c>
       <c r="O71">
-        <v>6.863080254999996</v>
+        <v>6.777617649999997</v>
       </c>
       <c r="P71">
-        <v>23.6394986561111</v>
+        <v>23.3451274611111</v>
       </c>
       <c r="Q71">
-        <v>45.03949865611109</v>
+        <v>44.7451274611111</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4110133922086938</v>
+        <v>0.4221819974750147</v>
       </c>
       <c r="T71">
-        <v>2.546429397435609</v>
+        <v>2.624301856072783</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.163841556571836</v>
+        <v>2.132929534335096</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1677760992425044</v>
+        <v>0.1676039969003137</v>
       </c>
       <c r="C72">
-        <v>224.8674421654677</v>
+        <v>220.5673476730379</v>
       </c>
       <c r="D72">
-        <v>503.1374421654677</v>
+        <v>503.848347673038</v>
       </c>
       <c r="E72">
-        <v>176.77</v>
+        <v>181.7810000000001</v>
       </c>
       <c r="F72">
-        <v>350.77</v>
+        <v>355.7810000000001</v>
       </c>
       <c r="G72">
         <v>72.5</v>
@@ -7191,28 +7191,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M72">
-        <v>26.588366</v>
+        <v>26.96819980000001</v>
       </c>
       <c r="N72">
-        <v>30.1227451111111</v>
+        <v>29.74291131111109</v>
       </c>
       <c r="O72">
-        <v>6.777617649999997</v>
+        <v>6.692155044999996</v>
       </c>
       <c r="P72">
-        <v>23.3451274611111</v>
+        <v>23.0507562661111</v>
       </c>
       <c r="Q72">
-        <v>44.7451274611111</v>
+        <v>44.4507562661111</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.4221819974750147</v>
+        <v>0.4341208513803922</v>
       </c>
       <c r="T72">
-        <v>2.624301856072783</v>
+        <v>2.707544829098728</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.132929534335096</v>
+        <v>2.102888273288122</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1676039969003137</v>
+        <v>0.1674318945581231</v>
       </c>
       <c r="C73">
-        <v>220.567347673038</v>
+        <v>216.2692649638392</v>
       </c>
       <c r="D73">
-        <v>503.8483476730379</v>
+        <v>504.5612649638392</v>
       </c>
       <c r="E73">
-        <v>181.781</v>
+        <v>186.792</v>
       </c>
       <c r="F73">
-        <v>355.781</v>
+        <v>360.792</v>
       </c>
       <c r="G73">
         <v>72.5</v>
@@ -7273,28 +7273,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M73">
-        <v>26.9681998</v>
+        <v>27.3480336</v>
       </c>
       <c r="N73">
-        <v>29.7429113111111</v>
+        <v>29.3630775111111</v>
       </c>
       <c r="O73">
-        <v>6.692155044999997</v>
+        <v>6.606692439999997</v>
       </c>
       <c r="P73">
-        <v>23.0507562661111</v>
+        <v>22.7563850711111</v>
       </c>
       <c r="Q73">
-        <v>44.4507562661111</v>
+        <v>44.1563850711111</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4341208513803921</v>
+        <v>0.4469124805647252</v>
       </c>
       <c r="T73">
-        <v>2.707544829098728</v>
+        <v>2.796733728769384</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.102888273288123</v>
+        <v>2.073681491714677</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1674318945581231</v>
+        <v>0.1672597922159324</v>
       </c>
       <c r="C74">
-        <v>216.2692649638392</v>
+        <v>211.9732025896554</v>
       </c>
       <c r="D74">
-        <v>504.5612649638392</v>
+        <v>505.2762025896554</v>
       </c>
       <c r="E74">
-        <v>186.792</v>
+        <v>191.803</v>
       </c>
       <c r="F74">
-        <v>360.792</v>
+        <v>365.803</v>
       </c>
       <c r="G74">
         <v>72.5</v>
@@ -7355,28 +7355,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M74">
-        <v>27.3480336</v>
+        <v>27.7278674</v>
       </c>
       <c r="N74">
-        <v>29.3630775111111</v>
+        <v>28.9832437111111</v>
       </c>
       <c r="O74">
-        <v>6.606692439999997</v>
+        <v>6.521229834999998</v>
       </c>
       <c r="P74">
-        <v>22.7563850711111</v>
+        <v>22.4620138761111</v>
       </c>
       <c r="Q74">
-        <v>44.1563850711111</v>
+        <v>43.8620138761111</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4469124805647252</v>
+        <v>0.4606516378367865</v>
       </c>
       <c r="T74">
-        <v>2.796733728769384</v>
+        <v>2.892529213600828</v>
       </c>
       <c r="U74">
         <v>0.07580000000000001</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>2.073681491714677</v>
+        <v>2.045274895937763</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1672597922159324</v>
+        <v>0.1670876898737417</v>
       </c>
       <c r="C75">
-        <v>211.9732025896554</v>
+        <v>207.6791691508076</v>
       </c>
       <c r="D75">
-        <v>505.2762025896554</v>
+        <v>505.9931691508076</v>
       </c>
       <c r="E75">
-        <v>191.803</v>
+        <v>196.814</v>
       </c>
       <c r="F75">
-        <v>365.803</v>
+        <v>370.814</v>
       </c>
       <c r="G75">
         <v>72.5</v>
@@ -7437,28 +7437,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M75">
-        <v>27.7278674</v>
+        <v>28.1077012</v>
       </c>
       <c r="N75">
-        <v>28.9832437111111</v>
+        <v>28.6034099111111</v>
       </c>
       <c r="O75">
-        <v>6.521229834999998</v>
+        <v>6.435767229999997</v>
       </c>
       <c r="P75">
-        <v>22.4620138761111</v>
+        <v>22.1676426811111</v>
       </c>
       <c r="Q75">
-        <v>43.8620138761111</v>
+        <v>43.5676426811111</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4606516378367865</v>
+        <v>0.475447653360545</v>
       </c>
       <c r="T75">
-        <v>2.892529213600828</v>
+        <v>2.995693581880845</v>
       </c>
       <c r="U75">
         <v>0.07580000000000001</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.045274895937763</v>
+        <v>2.017636045992658</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1670876898737417</v>
+        <v>0.1751693375315511</v>
       </c>
       <c r="C76">
-        <v>207.6791691508076</v>
+        <v>171.0589904353501</v>
       </c>
       <c r="D76">
-        <v>505.9931691508076</v>
+        <v>474.3839904353501</v>
       </c>
       <c r="E76">
-        <v>196.814</v>
+        <v>201.825</v>
       </c>
       <c r="F76">
-        <v>370.814</v>
+        <v>375.825</v>
       </c>
       <c r="G76">
         <v>72.5</v>
@@ -7519,45 +7519,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M76">
-        <v>28.1077012</v>
+        <v>33.82425000000001</v>
       </c>
       <c r="N76">
-        <v>28.6034099111111</v>
+        <v>22.8868611111111</v>
       </c>
       <c r="O76">
-        <v>6.435767229999997</v>
+        <v>5.149543749999997</v>
       </c>
       <c r="P76">
-        <v>22.1676426811111</v>
+        <v>17.7373173611111</v>
       </c>
       <c r="Q76">
-        <v>43.5676426811111</v>
+        <v>39.1373173611111</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.475447653360545</v>
+        <v>0.4914273501262043</v>
       </c>
       <c r="T76">
-        <v>2.995693581880845</v>
+        <v>3.107111099623265</v>
       </c>
       <c r="U76">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V76">
         <v>0.225</v>
       </c>
       <c r="W76">
-        <v>0.05874500000000001</v>
+        <v>0.06974999999999999</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y76">
-        <v>2.017636045992658</v>
+        <v>1.676640608767706</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1751693375315511</v>
+        <v>0.1751072851893604</v>
       </c>
       <c r="C77">
-        <v>171.0589904353501</v>
+        <v>166.2756391533721</v>
       </c>
       <c r="D77">
-        <v>474.3839904353501</v>
+        <v>474.6116391533722</v>
       </c>
       <c r="E77">
-        <v>201.825</v>
+        <v>206.836</v>
       </c>
       <c r="F77">
-        <v>375.825</v>
+        <v>380.836</v>
       </c>
       <c r="G77">
         <v>72.5</v>
@@ -7601,28 +7601,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M77">
-        <v>33.82425000000001</v>
+        <v>34.27524</v>
       </c>
       <c r="N77">
-        <v>22.8868611111111</v>
+        <v>22.4358711111111</v>
       </c>
       <c r="O77">
-        <v>5.149543749999997</v>
+        <v>5.048070999999998</v>
       </c>
       <c r="P77">
-        <v>17.7373173611111</v>
+        <v>17.3878001111111</v>
       </c>
       <c r="Q77">
-        <v>39.1373173611111</v>
+        <v>38.7878001111111</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4914273501262043</v>
+        <v>0.5087386882890017</v>
       </c>
       <c r="T77">
-        <v>3.107111099623265</v>
+        <v>3.227813410510886</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.676640608767706</v>
+        <v>1.654579548126026</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1751072851893604</v>
+        <v>0.1750452328471697</v>
       </c>
       <c r="C78">
-        <v>166.2756391533721</v>
+        <v>161.4925064657027</v>
       </c>
       <c r="D78">
-        <v>474.6116391533722</v>
+        <v>474.8395064657027</v>
       </c>
       <c r="E78">
-        <v>206.836</v>
+        <v>211.847</v>
       </c>
       <c r="F78">
-        <v>380.836</v>
+        <v>385.847</v>
       </c>
       <c r="G78">
         <v>72.5</v>
@@ -7683,28 +7683,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M78">
-        <v>34.27524</v>
+        <v>34.72623</v>
       </c>
       <c r="N78">
-        <v>22.4358711111111</v>
+        <v>21.9848811111111</v>
       </c>
       <c r="O78">
-        <v>5.048070999999998</v>
+        <v>4.946598249999997</v>
       </c>
       <c r="P78">
-        <v>17.3878001111111</v>
+        <v>17.0382828611111</v>
       </c>
       <c r="Q78">
-        <v>38.7878001111111</v>
+        <v>38.43828286111111</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.5087386882890017</v>
+        <v>0.5275553602050858</v>
       </c>
       <c r="T78">
-        <v>3.227813410510886</v>
+        <v>3.359011574519169</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.654579548126026</v>
+        <v>1.633091502046467</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1750452328471697</v>
+        <v>0.174983180504979</v>
       </c>
       <c r="C79">
-        <v>161.4925064657027</v>
+        <v>156.709592687343</v>
       </c>
       <c r="D79">
-        <v>474.8395064657027</v>
+        <v>475.067592687343</v>
       </c>
       <c r="E79">
-        <v>211.847</v>
+        <v>216.858</v>
       </c>
       <c r="F79">
-        <v>385.847</v>
+        <v>390.858</v>
       </c>
       <c r="G79">
         <v>72.5</v>
@@ -7765,28 +7765,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M79">
-        <v>34.72623</v>
+        <v>35.17722</v>
       </c>
       <c r="N79">
-        <v>21.9848811111111</v>
+        <v>21.5338911111111</v>
       </c>
       <c r="O79">
-        <v>4.946598249999997</v>
+        <v>4.845125499999998</v>
       </c>
       <c r="P79">
-        <v>17.0382828611111</v>
+        <v>16.6887656111111</v>
       </c>
       <c r="Q79">
-        <v>38.43828286111111</v>
+        <v>38.0887656111111</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5275553602050858</v>
+        <v>0.5480826386589958</v>
       </c>
       <c r="T79">
-        <v>3.359011574519169</v>
+        <v>3.502136844346387</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.633091502046467</v>
+        <v>1.61215443150741</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.174983180504979</v>
+        <v>0.1749211281627884</v>
       </c>
       <c r="C80">
-        <v>156.709592687343</v>
+        <v>151.9268981338997</v>
       </c>
       <c r="D80">
-        <v>475.067592687343</v>
+        <v>475.2958981338998</v>
       </c>
       <c r="E80">
-        <v>216.858</v>
+        <v>221.869</v>
       </c>
       <c r="F80">
-        <v>390.858</v>
+        <v>395.869</v>
       </c>
       <c r="G80">
         <v>72.5</v>
@@ -7847,28 +7847,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M80">
-        <v>35.17722</v>
+        <v>35.62821</v>
       </c>
       <c r="N80">
-        <v>21.5338911111111</v>
+        <v>21.0829011111111</v>
       </c>
       <c r="O80">
-        <v>4.845125499999998</v>
+        <v>4.743652749999997</v>
       </c>
       <c r="P80">
-        <v>16.6887656111111</v>
+        <v>16.3392483611111</v>
       </c>
       <c r="Q80">
-        <v>38.0887656111111</v>
+        <v>37.7392483611111</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5480826386589958</v>
+        <v>0.5705648960132782</v>
       </c>
       <c r="T80">
-        <v>3.502136844346387</v>
+        <v>3.658893092252388</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.61215443150741</v>
+        <v>1.591747413387063</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1749211281627884</v>
+        <v>0.1748590758205977</v>
       </c>
       <c r="C81">
-        <v>151.9268981338997</v>
+        <v>147.144423121587</v>
       </c>
       <c r="D81">
-        <v>475.2958981338998</v>
+        <v>475.5244231215871</v>
       </c>
       <c r="E81">
-        <v>221.869</v>
+        <v>226.8800000000001</v>
       </c>
       <c r="F81">
-        <v>395.869</v>
+        <v>400.8800000000001</v>
       </c>
       <c r="G81">
         <v>72.5</v>
@@ -7929,28 +7929,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M81">
-        <v>35.62821</v>
+        <v>36.0792</v>
       </c>
       <c r="N81">
-        <v>21.0829011111111</v>
+        <v>20.6319111111111</v>
       </c>
       <c r="O81">
-        <v>4.743652749999997</v>
+        <v>4.642179999999998</v>
       </c>
       <c r="P81">
-        <v>16.3392483611111</v>
+        <v>15.9897311111111</v>
       </c>
       <c r="Q81">
-        <v>37.7392483611111</v>
+        <v>37.3897311111111</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5705648960132782</v>
+        <v>0.5952953791029888</v>
       </c>
       <c r="T81">
-        <v>3.658893092252388</v>
+        <v>3.83132496494899</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.591747413387063</v>
+        <v>1.571850570719725</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1748590758205977</v>
+        <v>0.1747970234784071</v>
       </c>
       <c r="C82">
-        <v>147.144423121587</v>
+        <v>142.3621679672268</v>
       </c>
       <c r="D82">
-        <v>475.5244231215871</v>
+        <v>475.7531679672268</v>
       </c>
       <c r="E82">
-        <v>226.8800000000001</v>
+        <v>231.891</v>
       </c>
       <c r="F82">
-        <v>400.8800000000001</v>
+        <v>405.891</v>
       </c>
       <c r="G82">
         <v>72.5</v>
@@ -8011,28 +8011,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M82">
-        <v>36.0792</v>
+        <v>36.53019</v>
       </c>
       <c r="N82">
-        <v>20.6319111111111</v>
+        <v>20.1809211111111</v>
       </c>
       <c r="O82">
-        <v>4.642179999999998</v>
+        <v>4.540707249999999</v>
       </c>
       <c r="P82">
-        <v>15.9897311111111</v>
+        <v>15.64021386111111</v>
       </c>
       <c r="Q82">
-        <v>37.3897311111111</v>
+        <v>37.04021386111111</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5952953791029888</v>
+        <v>0.6226290709389847</v>
       </c>
       <c r="T82">
-        <v>3.83132496494899</v>
+        <v>4.021907561087337</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.571850570719725</v>
+        <v>1.552445008118247</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1747970234784071</v>
+        <v>0.1747349711362164</v>
       </c>
       <c r="C83">
-        <v>142.3621679672268</v>
+        <v>137.5801329882513</v>
       </c>
       <c r="D83">
-        <v>475.7531679672268</v>
+        <v>475.9821329882513</v>
       </c>
       <c r="E83">
-        <v>231.891</v>
+        <v>236.902</v>
       </c>
       <c r="F83">
-        <v>405.891</v>
+        <v>410.902</v>
       </c>
       <c r="G83">
         <v>72.5</v>
@@ -8093,28 +8093,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M83">
-        <v>36.53019</v>
+        <v>36.98118</v>
       </c>
       <c r="N83">
-        <v>20.1809211111111</v>
+        <v>19.7299311111111</v>
       </c>
       <c r="O83">
-        <v>4.540707249999999</v>
+        <v>4.439234499999998</v>
       </c>
       <c r="P83">
-        <v>15.64021386111111</v>
+        <v>15.2906966111111</v>
       </c>
       <c r="Q83">
-        <v>37.04021386111111</v>
+        <v>36.6906966111111</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.6226290709389847</v>
+        <v>0.6529998396456469</v>
       </c>
       <c r="T83">
-        <v>4.021907561087337</v>
+        <v>4.233666001241058</v>
       </c>
       <c r="U83">
         <v>0.09</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>1.552445008118247</v>
+        <v>1.533512751921683</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1747349711362164</v>
+        <v>0.1746729187940257</v>
       </c>
       <c r="C84">
-        <v>137.5801329882513</v>
+        <v>132.7983185027039</v>
       </c>
       <c r="D84">
-        <v>475.9821329882513</v>
+        <v>476.2113185027039</v>
       </c>
       <c r="E84">
-        <v>236.902</v>
+        <v>241.9130000000001</v>
       </c>
       <c r="F84">
-        <v>410.902</v>
+        <v>415.9130000000001</v>
       </c>
       <c r="G84">
         <v>72.5</v>
@@ -8175,28 +8175,28 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M84">
-        <v>36.98118</v>
+        <v>37.43217000000001</v>
       </c>
       <c r="N84">
-        <v>19.7299311111111</v>
+        <v>19.2789411111111</v>
       </c>
       <c r="O84">
-        <v>4.439234499999998</v>
+        <v>4.337761749999997</v>
       </c>
       <c r="P84">
-        <v>15.2906966111111</v>
+        <v>14.9411793611111</v>
       </c>
       <c r="Q84">
-        <v>36.6906966111111</v>
+        <v>36.3411793611111</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6529998396456469</v>
+        <v>0.6869436399648575</v>
       </c>
       <c r="T84">
-        <v>4.233666001241058</v>
+        <v>4.470337199059922</v>
       </c>
       <c r="U84">
         <v>0.09</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>1.533512751921683</v>
+        <v>1.515036694669614</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1746729187940257</v>
+        <v>0.2159515619307451</v>
       </c>
       <c r="C85">
-        <v>132.7983185027039</v>
+        <v>12.25880468194549</v>
       </c>
       <c r="D85">
-        <v>476.2113185027039</v>
+        <v>360.6828046819455</v>
       </c>
       <c r="E85">
-        <v>241.9130000000001</v>
+        <v>246.924</v>
       </c>
       <c r="F85">
-        <v>415.9130000000001</v>
+        <v>420.924</v>
       </c>
       <c r="G85">
         <v>72.5</v>
@@ -8257,45 +8257,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M85">
-        <v>37.43217000000001</v>
+        <v>61.79164320000001</v>
       </c>
       <c r="N85">
-        <v>19.2789411111111</v>
+        <v>-5.080532088888909</v>
       </c>
       <c r="O85">
-        <v>4.337761749999997</v>
+        <v>-1.143119720000005</v>
       </c>
       <c r="P85">
-        <v>14.9411793611111</v>
+        <v>-3.937412368888904</v>
       </c>
       <c r="Q85">
-        <v>36.3411793611111</v>
+        <v>17.4625876311111</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6869436399648575</v>
+        <v>0.7381471323525292</v>
       </c>
       <c r="T85">
-        <v>4.470337199059922</v>
+        <v>4.827350608340464</v>
       </c>
       <c r="U85">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.225</v>
+        <v>0.2065004155772313</v>
       </c>
       <c r="W85">
-        <v>0.06974999999999999</v>
+        <v>0.1164857389932625</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y85">
-        <v>1.515036694669614</v>
+        <v>0.9177796247876945</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2159515619307451</v>
+        <v>0.2169615619307451</v>
       </c>
       <c r="C86">
-        <v>12.25880468194561</v>
+        <v>5.119466820223124</v>
       </c>
       <c r="D86">
-        <v>360.6828046819456</v>
+        <v>358.5544668202231</v>
       </c>
       <c r="E86">
-        <v>246.924</v>
+        <v>251.935</v>
       </c>
       <c r="F86">
-        <v>420.924</v>
+        <v>425.935</v>
       </c>
       <c r="G86">
         <v>72.5</v>
@@ -8339,37 +8339,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M86">
-        <v>61.7916432</v>
+        <v>62.527258</v>
       </c>
       <c r="N86">
-        <v>-5.080532088888901</v>
+        <v>-5.816146888888902</v>
       </c>
       <c r="O86">
-        <v>-1.143119720000003</v>
+        <v>-1.308633050000003</v>
       </c>
       <c r="P86">
-        <v>-3.937412368888898</v>
+        <v>-4.507513838888899</v>
       </c>
       <c r="Q86">
-        <v>17.4625876311111</v>
+        <v>16.8924861611111</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7381471323525287</v>
+        <v>0.7843036078426974</v>
       </c>
       <c r="T86">
-        <v>4.827350608340462</v>
+        <v>5.149173982229826</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2065004155772313</v>
+        <v>0.2040709989233815</v>
       </c>
       <c r="W86">
-        <v>0.1164857389932624</v>
+        <v>0.1168423773580476</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.9177796247876946</v>
+        <v>0.906982217437251</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2169615619307451</v>
+        <v>0.2179715619307451</v>
       </c>
       <c r="C87">
-        <v>5.119466820223124</v>
+        <v>-1.994900352772049</v>
       </c>
       <c r="D87">
-        <v>358.5544668202231</v>
+        <v>356.451099647228</v>
       </c>
       <c r="E87">
-        <v>251.935</v>
+        <v>256.946</v>
       </c>
       <c r="F87">
-        <v>425.935</v>
+        <v>430.946</v>
       </c>
       <c r="G87">
         <v>72.5</v>
@@ -8421,37 +8421,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M87">
-        <v>62.527258</v>
+        <v>63.26287280000001</v>
       </c>
       <c r="N87">
-        <v>-5.816146888888902</v>
+        <v>-6.551761688888909</v>
       </c>
       <c r="O87">
-        <v>-1.308633050000003</v>
+        <v>-1.474146380000005</v>
       </c>
       <c r="P87">
-        <v>-4.507513838888899</v>
+        <v>-5.077615308888904</v>
       </c>
       <c r="Q87">
-        <v>16.8924861611111</v>
+        <v>16.32238469111109</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7843036078426974</v>
+        <v>0.8370538655457472</v>
       </c>
       <c r="T87">
-        <v>5.149173982229826</v>
+        <v>5.516972123817671</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2040709989233815</v>
+        <v>0.2016980803312491</v>
       </c>
       <c r="W87">
-        <v>0.1168423773580476</v>
+        <v>0.1171907218073726</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.906982217437251</v>
+        <v>0.8964359125833294</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2179715619307451</v>
+        <v>0.2189815619307451</v>
       </c>
       <c r="C88">
-        <v>-1.994900352772049</v>
+        <v>-9.084733726429135</v>
       </c>
       <c r="D88">
-        <v>356.451099647228</v>
+        <v>354.3722662735709</v>
       </c>
       <c r="E88">
-        <v>256.946</v>
+        <v>261.957</v>
       </c>
       <c r="F88">
-        <v>430.946</v>
+        <v>435.957</v>
       </c>
       <c r="G88">
         <v>72.5</v>
@@ -8503,37 +8503,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M88">
-        <v>63.26287280000001</v>
+        <v>63.9984876</v>
       </c>
       <c r="N88">
-        <v>-6.551761688888909</v>
+        <v>-7.287376488888903</v>
       </c>
       <c r="O88">
-        <v>-1.474146380000005</v>
+        <v>-1.639659710000003</v>
       </c>
       <c r="P88">
-        <v>-5.077615308888904</v>
+        <v>-5.647716778888899</v>
       </c>
       <c r="Q88">
-        <v>16.32238469111109</v>
+        <v>15.7522832211111</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8370538655457472</v>
+        <v>0.8979195475108047</v>
       </c>
       <c r="T88">
-        <v>5.516972123817671</v>
+        <v>5.941354594880568</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2016980803312491</v>
+        <v>0.1993797115918095</v>
       </c>
       <c r="W88">
-        <v>0.1171907218073726</v>
+        <v>0.1175310583383224</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8964359125833294</v>
+        <v>0.8861320515191533</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2189815619307451</v>
+        <v>0.2199915619307451</v>
       </c>
       <c r="C89">
-        <v>-9.084733726429135</v>
+        <v>-16.15046005742448</v>
       </c>
       <c r="D89">
-        <v>354.3722662735709</v>
+        <v>352.3175399425755</v>
       </c>
       <c r="E89">
-        <v>261.957</v>
+        <v>266.968</v>
       </c>
       <c r="F89">
-        <v>435.957</v>
+        <v>440.968</v>
       </c>
       <c r="G89">
         <v>72.5</v>
@@ -8585,37 +8585,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M89">
-        <v>63.9984876</v>
+        <v>64.73410240000001</v>
       </c>
       <c r="N89">
-        <v>-7.287376488888903</v>
+        <v>-8.02299128888891</v>
       </c>
       <c r="O89">
-        <v>-1.639659710000003</v>
+        <v>-1.805173040000005</v>
       </c>
       <c r="P89">
-        <v>-5.647716778888899</v>
+        <v>-6.217818248888905</v>
       </c>
       <c r="Q89">
-        <v>15.7522832211111</v>
+        <v>15.18218175111109</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8979195475108047</v>
+        <v>0.9689295098033718</v>
       </c>
       <c r="T89">
-        <v>5.941354594880568</v>
+        <v>6.436467477787283</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.1993797115918095</v>
+        <v>0.1971140330509935</v>
       </c>
       <c r="W89">
-        <v>0.1175310583383224</v>
+        <v>0.1178636599481142</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8861320515191533</v>
+        <v>0.8760623691155265</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2199915619307451</v>
+        <v>0.2210015619307451</v>
       </c>
       <c r="C90">
-        <v>-16.15046005742448</v>
+        <v>-23.19249626178595</v>
       </c>
       <c r="D90">
-        <v>352.3175399425755</v>
+        <v>350.2865037382141</v>
       </c>
       <c r="E90">
-        <v>266.968</v>
+        <v>271.979</v>
       </c>
       <c r="F90">
-        <v>440.968</v>
+        <v>445.979</v>
       </c>
       <c r="G90">
         <v>72.5</v>
@@ -8667,37 +8667,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M90">
-        <v>64.73410240000001</v>
+        <v>65.46971720000002</v>
       </c>
       <c r="N90">
-        <v>-8.02299128888891</v>
+        <v>-8.758606088888918</v>
       </c>
       <c r="O90">
-        <v>-1.805173040000005</v>
+        <v>-1.970686370000007</v>
       </c>
       <c r="P90">
-        <v>-6.217818248888905</v>
+        <v>-6.787919718888912</v>
       </c>
       <c r="Q90">
-        <v>15.18218175111109</v>
+        <v>14.61208028111109</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9689295098033718</v>
+        <v>1.052850374330951</v>
       </c>
       <c r="T90">
-        <v>6.436467477787283</v>
+        <v>7.021600884858855</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.1971140330509935</v>
+        <v>0.1948992686346901</v>
       </c>
       <c r="W90">
-        <v>0.1178636599481142</v>
+        <v>0.1181887873644275</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8760623691155265</v>
+        <v>0.8662189717097339</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2210015619307451</v>
+        <v>0.2220115619307451</v>
       </c>
       <c r="C91">
-        <v>-23.19249626178595</v>
+        <v>-30.21124969691317</v>
       </c>
       <c r="D91">
-        <v>350.2865037382141</v>
+        <v>348.2787503030868</v>
       </c>
       <c r="E91">
-        <v>271.979</v>
+        <v>276.99</v>
       </c>
       <c r="F91">
-        <v>445.979</v>
+        <v>450.99</v>
       </c>
       <c r="G91">
         <v>72.5</v>
@@ -8749,37 +8749,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M91">
-        <v>65.46971720000002</v>
+        <v>66.20533200000001</v>
       </c>
       <c r="N91">
-        <v>-8.758606088888918</v>
+        <v>-9.494220888888911</v>
       </c>
       <c r="O91">
-        <v>-1.970686370000007</v>
+        <v>-2.136199700000005</v>
       </c>
       <c r="P91">
-        <v>-6.787919718888912</v>
+        <v>-7.358021188888906</v>
       </c>
       <c r="Q91">
-        <v>14.61208028111109</v>
+        <v>14.04197881111109</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>1.052850374330951</v>
+        <v>1.153555411764047</v>
       </c>
       <c r="T91">
-        <v>7.021600884858855</v>
+        <v>7.723760973344741</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.1948992686346901</v>
+        <v>0.1927337212054158</v>
       </c>
       <c r="W91">
-        <v>0.1181887873644275</v>
+        <v>0.118506689727045</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8662189717097339</v>
+        <v>0.8565943164685148</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2220115619307451</v>
+        <v>0.2230215619307451</v>
       </c>
       <c r="C92">
-        <v>-30.21124969691317</v>
+        <v>-37.20711843395532</v>
       </c>
       <c r="D92">
-        <v>348.2787503030868</v>
+        <v>346.2938815660447</v>
       </c>
       <c r="E92">
-        <v>276.99</v>
+        <v>282.001</v>
       </c>
       <c r="F92">
-        <v>450.99</v>
+        <v>456.001</v>
       </c>
       <c r="G92">
         <v>72.5</v>
@@ -8831,37 +8831,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M92">
-        <v>66.20533200000001</v>
+        <v>66.94094680000001</v>
       </c>
       <c r="N92">
-        <v>-9.494220888888911</v>
+        <v>-10.2298356888889</v>
       </c>
       <c r="O92">
-        <v>-2.136199700000005</v>
+        <v>-2.301713030000004</v>
       </c>
       <c r="P92">
-        <v>-7.358021188888906</v>
+        <v>-7.928122658888901</v>
       </c>
       <c r="Q92">
-        <v>14.04197881111109</v>
+        <v>13.4718773411111</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.153555411764047</v>
+        <v>1.276639346404496</v>
       </c>
       <c r="T92">
-        <v>7.723760973344741</v>
+        <v>8.581956637049712</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.1927337212054158</v>
+        <v>0.1906157682251366</v>
       </c>
       <c r="W92">
-        <v>0.118506689727045</v>
+        <v>0.11881760522455</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8565943164685148</v>
+        <v>0.8471811921117181</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2230215619307451</v>
+        <v>0.2240315619307451</v>
       </c>
       <c r="C93">
-        <v>-37.20711843395532</v>
+        <v>-44.18049152092635</v>
       </c>
       <c r="D93">
-        <v>346.2938815660447</v>
+        <v>344.3315084790737</v>
       </c>
       <c r="E93">
-        <v>282.001</v>
+        <v>287.0120000000001</v>
       </c>
       <c r="F93">
-        <v>456.001</v>
+        <v>461.0120000000001</v>
       </c>
       <c r="G93">
         <v>72.5</v>
@@ -8913,37 +8913,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M93">
-        <v>66.94094680000001</v>
+        <v>67.67656160000001</v>
       </c>
       <c r="N93">
-        <v>-10.2298356888889</v>
+        <v>-10.96545048888891</v>
       </c>
       <c r="O93">
-        <v>-2.301713030000004</v>
+        <v>-2.467226360000006</v>
       </c>
       <c r="P93">
-        <v>-7.928122658888901</v>
+        <v>-8.498224128888907</v>
       </c>
       <c r="Q93">
-        <v>13.4718773411111</v>
+        <v>12.90177587111109</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.276639346404496</v>
+        <v>1.430494264705058</v>
       </c>
       <c r="T93">
-        <v>8.581956637049712</v>
+        <v>9.654701216680929</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.1906157682251366</v>
+        <v>0.1885438577009503</v>
       </c>
       <c r="W93">
-        <v>0.11881760522455</v>
+        <v>0.1191217616895005</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8471811921117181</v>
+        <v>0.8379727008931123</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2240315619307451</v>
+        <v>0.2250415619307451</v>
       </c>
       <c r="C94">
-        <v>-44.18049152092635</v>
+        <v>-51.13174923692554</v>
       </c>
       <c r="D94">
-        <v>344.3315084790737</v>
+        <v>342.3912507630745</v>
       </c>
       <c r="E94">
-        <v>287.0120000000001</v>
+        <v>292.023</v>
       </c>
       <c r="F94">
-        <v>461.0120000000001</v>
+        <v>466.023</v>
       </c>
       <c r="G94">
         <v>72.5</v>
@@ -8995,37 +8995,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M94">
-        <v>67.67656160000001</v>
+        <v>68.41217640000001</v>
       </c>
       <c r="N94">
-        <v>-10.96545048888891</v>
+        <v>-11.70106528888891</v>
       </c>
       <c r="O94">
-        <v>-2.467226360000006</v>
+        <v>-2.632739690000004</v>
       </c>
       <c r="P94">
-        <v>-8.498224128888907</v>
+        <v>-9.068325598888901</v>
       </c>
       <c r="Q94">
-        <v>12.90177587111109</v>
+        <v>12.3316744011111</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.430494264705058</v>
+        <v>1.628307731091496</v>
       </c>
       <c r="T94">
-        <v>9.654701216680929</v>
+        <v>11.03394424763535</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.1885438577009503</v>
+        <v>0.1865165043923379</v>
       </c>
       <c r="W94">
-        <v>0.1191217616895005</v>
+        <v>0.1194193771552048</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8379727008931123</v>
+        <v>0.8289622417437241</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2250415619307451</v>
+        <v>0.2260515619307451</v>
       </c>
       <c r="C95">
-        <v>-51.13174923692554</v>
+        <v>-58.0612633378106</v>
       </c>
       <c r="D95">
-        <v>342.3912507630745</v>
+        <v>340.4727366621894</v>
       </c>
       <c r="E95">
-        <v>292.023</v>
+        <v>297.034</v>
       </c>
       <c r="F95">
-        <v>466.023</v>
+        <v>471.034</v>
       </c>
       <c r="G95">
         <v>72.5</v>
@@ -9077,37 +9077,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M95">
-        <v>68.41217640000001</v>
+        <v>69.14779120000001</v>
       </c>
       <c r="N95">
-        <v>-11.70106528888891</v>
+        <v>-12.43668008888891</v>
       </c>
       <c r="O95">
-        <v>-2.632739690000004</v>
+        <v>-2.798253020000006</v>
       </c>
       <c r="P95">
-        <v>-9.068325598888901</v>
+        <v>-9.638427068888907</v>
       </c>
       <c r="Q95">
-        <v>12.3316744011111</v>
+        <v>11.76157293111109</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.628307731091496</v>
+        <v>1.892059019606745</v>
       </c>
       <c r="T95">
-        <v>11.03394424763535</v>
+        <v>12.87293495557458</v>
       </c>
       <c r="U95">
         <v>0.1468</v>
       </c>
       <c r="V95">
-        <v>0.1865165043923379</v>
+        <v>0.1845322862605045</v>
       </c>
       <c r="W95">
-        <v>0.1194193771552048</v>
+        <v>0.1197106603769579</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.8289622417437241</v>
+        <v>0.8201434944911312</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2260515619307451</v>
+        <v>0.2270615619307451</v>
       </c>
       <c r="C96">
-        <v>-58.0612633378106</v>
+        <v>-64.96939729365846</v>
       </c>
       <c r="D96">
-        <v>340.4727366621894</v>
+        <v>338.5756027063416</v>
       </c>
       <c r="E96">
-        <v>297.034</v>
+        <v>302.0450000000001</v>
       </c>
       <c r="F96">
-        <v>471.034</v>
+        <v>476.0450000000001</v>
       </c>
       <c r="G96">
         <v>72.5</v>
@@ -9159,37 +9159,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M96">
-        <v>69.14779120000001</v>
+        <v>69.88340600000002</v>
       </c>
       <c r="N96">
-        <v>-12.43668008888891</v>
+        <v>-13.17229488888892</v>
       </c>
       <c r="O96">
-        <v>-2.798253020000006</v>
+        <v>-2.963766350000007</v>
       </c>
       <c r="P96">
-        <v>-9.638427068888907</v>
+        <v>-10.20852853888891</v>
       </c>
       <c r="Q96">
-        <v>11.76157293111109</v>
+        <v>11.19147146111109</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.892059019606745</v>
+        <v>2.261310823528095</v>
       </c>
       <c r="T96">
-        <v>12.87293495557458</v>
+        <v>15.4475219466895</v>
       </c>
       <c r="U96">
         <v>0.1468</v>
       </c>
       <c r="V96">
-        <v>0.1845322862605045</v>
+        <v>0.1825898411419729</v>
       </c>
       <c r="W96">
-        <v>0.1197106603769579</v>
+        <v>0.1199958113203584</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.8201434944911312</v>
+        <v>0.8115104050754349</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2270615619307451</v>
+        <v>0.2280715619307451</v>
       </c>
       <c r="C97">
-        <v>-64.96939729365846</v>
+        <v>-71.85650651832907</v>
       </c>
       <c r="D97">
-        <v>338.5756027063416</v>
+        <v>336.699493481671</v>
       </c>
       <c r="E97">
-        <v>302.0450000000001</v>
+        <v>307.056</v>
       </c>
       <c r="F97">
-        <v>476.0450000000001</v>
+        <v>481.056</v>
       </c>
       <c r="G97">
         <v>72.5</v>
@@ -9241,37 +9241,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M97">
-        <v>69.88340600000002</v>
+        <v>70.61902080000002</v>
       </c>
       <c r="N97">
-        <v>-13.17229488888892</v>
+        <v>-13.90790968888891</v>
       </c>
       <c r="O97">
-        <v>-2.963766350000007</v>
+        <v>-3.129279680000006</v>
       </c>
       <c r="P97">
-        <v>-10.20852853888891</v>
+        <v>-10.77863000888891</v>
       </c>
       <c r="Q97">
-        <v>11.19147146111109</v>
+        <v>10.62136999111109</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.261310823528095</v>
+        <v>2.81518852941012</v>
       </c>
       <c r="T97">
-        <v>15.4475219466895</v>
+        <v>19.30940243336188</v>
       </c>
       <c r="U97">
         <v>0.1468</v>
       </c>
       <c r="V97">
-        <v>0.1825898411419729</v>
+        <v>0.1806878636300774</v>
       </c>
       <c r="W97">
-        <v>0.1199958113203584</v>
+        <v>0.1202750216191047</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.8115104050754349</v>
+        <v>0.8030571716892326</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2280715619307451</v>
+        <v>0.2877134393662535</v>
       </c>
       <c r="C98">
-        <v>-71.85650651832901</v>
+        <v>-159.8781485704584</v>
       </c>
       <c r="D98">
-        <v>336.699493481671</v>
+        <v>253.6888514295416</v>
       </c>
       <c r="E98">
-        <v>307.056</v>
+        <v>312.067</v>
       </c>
       <c r="F98">
-        <v>481.056</v>
+        <v>486.067</v>
       </c>
       <c r="G98">
         <v>72.5</v>
@@ -9323,45 +9323,45 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M98">
-        <v>70.6190208</v>
+        <v>97.60225360000001</v>
       </c>
       <c r="N98">
-        <v>-13.9079096888889</v>
+        <v>-40.89114248888891</v>
       </c>
       <c r="O98">
-        <v>-3.129279680000002</v>
+        <v>-9.200507060000005</v>
       </c>
       <c r="P98">
-        <v>-10.7786300088889</v>
+        <v>-31.6906354288889</v>
       </c>
       <c r="Q98">
-        <v>10.6213699911111</v>
+        <v>-10.2906354288889</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.815188529410113</v>
+        <v>3.946713953730433</v>
       </c>
       <c r="T98">
-        <v>19.30940243336183</v>
+        <v>27.19889845378316</v>
       </c>
       <c r="U98">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1806878636300774</v>
+        <v>0.1307346862326957</v>
       </c>
       <c r="W98">
-        <v>0.1202750216191047</v>
+        <v>0.1745484750044747</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y98">
-        <v>0.8030571716892327</v>
+        <v>0.5810430499230921</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2877134393662535</v>
+        <v>0.2892634393662535</v>
       </c>
       <c r="C99">
-        <v>-159.8781485704584</v>
+        <v>-166.5042482369191</v>
       </c>
       <c r="D99">
-        <v>253.6888514295416</v>
+        <v>252.0737517630809</v>
       </c>
       <c r="E99">
-        <v>312.067</v>
+        <v>317.078</v>
       </c>
       <c r="F99">
-        <v>486.067</v>
+        <v>491.078</v>
       </c>
       <c r="G99">
         <v>72.5</v>
@@ -9405,37 +9405,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M99">
-        <v>97.60225360000001</v>
+        <v>98.60846240000001</v>
       </c>
       <c r="N99">
-        <v>-40.89114248888891</v>
+        <v>-41.89735128888891</v>
       </c>
       <c r="O99">
-        <v>-9.200507060000005</v>
+        <v>-9.426904040000004</v>
       </c>
       <c r="P99">
-        <v>-31.6906354288889</v>
+        <v>-32.4704472488889</v>
       </c>
       <c r="Q99">
-        <v>-10.2906354288889</v>
+        <v>-11.0704472488889</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.946713953730433</v>
+        <v>5.897170930595649</v>
       </c>
       <c r="T99">
-        <v>27.19889845378316</v>
+        <v>40.79834768067474</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1307346862326957</v>
+        <v>0.129400658822158</v>
       </c>
       <c r="W99">
-        <v>0.1745484750044747</v>
+        <v>0.1748163477085107</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5810430499230921</v>
+        <v>0.5751140392095913</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2892634393662535</v>
+        <v>0.2908134393662535</v>
       </c>
       <c r="C100">
-        <v>-166.5042482369191</v>
+        <v>-173.1099130693601</v>
       </c>
       <c r="D100">
-        <v>252.0737517630809</v>
+        <v>250.4790869306399</v>
       </c>
       <c r="E100">
-        <v>317.078</v>
+        <v>322.089</v>
       </c>
       <c r="F100">
-        <v>491.078</v>
+        <v>496.089</v>
       </c>
       <c r="G100">
         <v>72.5</v>
@@ -9487,37 +9487,37 @@
         <v>56.7111111111111</v>
       </c>
       <c r="M100">
-        <v>98.60846240000001</v>
+        <v>99.6146712</v>
       </c>
       <c r="N100">
-        <v>-41.89735128888891</v>
+        <v>-42.9035600888889</v>
       </c>
       <c r="O100">
-        <v>-9.426904040000004</v>
+        <v>-9.653301020000002</v>
       </c>
       <c r="P100">
-        <v>-32.4704472488889</v>
+        <v>-33.2502590688889</v>
       </c>
       <c r="Q100">
-        <v>-11.0704472488889</v>
+        <v>-11.8502590688889</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.897170930595649</v>
+        <v>11.7485418611913</v>
       </c>
       <c r="T100">
-        <v>40.79834768067474</v>
+        <v>81.59669536134948</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.129400658822158</v>
+        <v>0.128093581460318</v>
       </c>
       <c r="W100">
-        <v>0.1748163477085107</v>
+        <v>0.1750788088427681</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5751140392095913</v>
+        <v>0.5693048064903024</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2908134393662535</v>
-      </c>
-      <c r="C101">
-        <v>-173.1099130693601</v>
-      </c>
-      <c r="D101">
-        <v>250.4790869306399</v>
-      </c>
-      <c r="E101">
-        <v>322.089</v>
-      </c>
-      <c r="F101">
-        <v>496.089</v>
-      </c>
-      <c r="G101">
-        <v>72.5</v>
-      </c>
-      <c r="H101">
-        <v>327.1</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>78.1111111111111</v>
-      </c>
-      <c r="K101">
-        <v>21.4</v>
-      </c>
-      <c r="L101">
-        <v>56.7111111111111</v>
-      </c>
-      <c r="M101">
-        <v>99.6146712</v>
-      </c>
-      <c r="N101">
-        <v>-42.9035600888889</v>
-      </c>
-      <c r="O101">
-        <v>-9.653301020000002</v>
-      </c>
-      <c r="P101">
-        <v>-33.2502590688889</v>
-      </c>
-      <c r="Q101">
-        <v>-11.8502590688889</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>11.7485418611913</v>
-      </c>
-      <c r="T101">
-        <v>81.59669536134948</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.128093581460318</v>
-      </c>
-      <c r="W101">
-        <v>0.1750788088427681</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5693048064903024</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
